--- a/OrangeHRM-TestCase-V1.0.xlsx
+++ b/OrangeHRM-TestCase-V1.0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ME\Downloads\ManualTesting-OrangeHRM-master\ManualTesting-OrangeHRM-master\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ME\OneDrive - Nelson Mandela University\Documents\GitHub\ManualTesting-OrangeHRM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC32F081-B95A-47C1-B527-378F58918C03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D07D29FB-95BD-4BF8-BEB0-33F9E9C6BA22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{265E3A40-E9C7-654F-86F5-8DA790EB10BE}"/>
+    <workbookView xWindow="1830" yWindow="300" windowWidth="10725" windowHeight="10485" xr2:uid="{265E3A40-E9C7-654F-86F5-8DA790EB10BE}"/>
   </bookViews>
   <sheets>
     <sheet name="Version History" sheetId="4" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="806" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="806" uniqueCount="320">
   <si>
     <t>SNO</t>
   </si>
@@ -173,9 +173,6 @@
     <t>ESS user can upload multiple attchments</t>
   </si>
   <si>
-    <t>ESS user can delete attchments</t>
-  </si>
-  <si>
     <t>3.1.11</t>
   </si>
   <si>
@@ -228,9 +225,6 @@
   </si>
   <si>
     <t>Orange HRM-MyInfo</t>
-  </si>
-  <si>
-    <t>pavan@12345/pavan@12345</t>
   </si>
   <si>
     <t>TC_MyInfo_002</t>
@@ -286,18 +280,9 @@
 5. Click on Login button</t>
   </si>
   <si>
-    <t>pavan@12345/xxxxxx</t>
-  </si>
-  <si>
     <t>Invalid Credentials</t>
   </si>
   <si>
-    <t>xxxxxxxx/pavan@12345</t>
-  </si>
-  <si>
-    <t>xxxxxxxx/xxxxxx</t>
-  </si>
-  <si>
     <t>No. Of Test Cases</t>
   </si>
   <si>
@@ -328,28 +313,585 @@
     <t>Verify ESS user is able to view Personal Details</t>
   </si>
   <si>
-    <t>1. Login to Orange HM as ESS user
+    <t>Verify ESS user can edit Personal Details</t>
+  </si>
+  <si>
+    <t>User should be able to view Personal Details</t>
+  </si>
+  <si>
+    <t>Verify ESS user cannot edit restricted fields</t>
+  </si>
+  <si>
+    <t>TC_MyInfo_012</t>
+  </si>
+  <si>
+    <t>TC_MyInfo_013</t>
+  </si>
+  <si>
+    <t>TC_MyInfo_014</t>
+  </si>
+  <si>
+    <t>TC_MyInfo_015</t>
+  </si>
+  <si>
+    <t>Verify ESS is able to view Contacts Details</t>
+  </si>
+  <si>
+    <t>Verify ESS is able to edit Contacts Details</t>
+  </si>
+  <si>
+    <t>User should able to view Contact Details</t>
+  </si>
+  <si>
+    <t>User should be able to edit and save Contact Details</t>
+  </si>
+  <si>
+    <t>TC_MyInfo_016</t>
+  </si>
+  <si>
+    <t>TC_MyInfo_017</t>
+  </si>
+  <si>
+    <t>TC_MyInfo_018</t>
+  </si>
+  <si>
+    <t>TC_MyInfo_019</t>
+  </si>
+  <si>
+    <t>TC_MyInfo_020</t>
+  </si>
+  <si>
+    <t>TC_MyInfo_021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify ESS user is able to add Emergency Contact </t>
+  </si>
+  <si>
+    <t>TC_MyInfo_022</t>
+  </si>
+  <si>
+    <t>TC_MyInfo_023</t>
+  </si>
+  <si>
+    <t>TC_MyInfo_024</t>
+  </si>
+  <si>
+    <t>TC_MyInfo_025</t>
+  </si>
+  <si>
+    <t>TC_MyInfo_026</t>
+  </si>
+  <si>
+    <t>TC_MyInfo_027</t>
+  </si>
+  <si>
+    <t>TC_MyInfo_028</t>
+  </si>
+  <si>
+    <t>TC_MyInfo_029</t>
+  </si>
+  <si>
+    <t>TC_MyInfo_030</t>
+  </si>
+  <si>
+    <t>TC_MyInfo_031</t>
+  </si>
+  <si>
+    <t>TC_MyInfo_032</t>
+  </si>
+  <si>
+    <t>TC_MyInfo_033</t>
+  </si>
+  <si>
+    <t>TC_MyInfo_034</t>
+  </si>
+  <si>
+    <t>TC_MyInfo_035</t>
+  </si>
+  <si>
+    <t>TC_MyInfo_036</t>
+  </si>
+  <si>
+    <t>TC_MyInfo_037</t>
+  </si>
+  <si>
+    <t>TC_MyInfo_038</t>
+  </si>
+  <si>
+    <t>TC_MyInfo_039</t>
+  </si>
+  <si>
+    <t>TC_MyInfo_040</t>
+  </si>
+  <si>
+    <t>TC_MyInfo_041</t>
+  </si>
+  <si>
+    <t>TC_MyInfo_043</t>
+  </si>
+  <si>
+    <t>TC_MyInfo_044</t>
+  </si>
+  <si>
+    <t>TC_MyInfo_045</t>
+  </si>
+  <si>
+    <t>TC_MyInfo_046</t>
+  </si>
+  <si>
+    <t>Successful saved
+Details should be appeared under Emergency Contact table</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify ESS user is able to delete Emergency Contact </t>
+  </si>
+  <si>
+    <t>Verify ESS user is able to add Multiple Emergency Contacts</t>
+  </si>
+  <si>
+    <t>Successful saved
+Multiple details should be appeared under Emergency Contact table</t>
+  </si>
+  <si>
+    <t>Successful deleted
+Entries should disappear from Emergency Contacts table</t>
+  </si>
+  <si>
+    <t>Verify ESS user is able to delete Dependants</t>
+  </si>
+  <si>
+    <t>ESS User can attach documents under Emergency Contact</t>
+  </si>
+  <si>
+    <t>ESS user can add multiple Dependants</t>
+  </si>
+  <si>
+    <t>ESS user can add Dependants</t>
+  </si>
+  <si>
+    <t>Verify ESS User is able to attach documents under Emergency Contact</t>
+  </si>
+  <si>
+    <t>Successful upload file</t>
+  </si>
+  <si>
+    <t>TC_MyInfo_047</t>
+  </si>
+  <si>
+    <t>Verify ESS user is able to add Dependants</t>
+  </si>
+  <si>
+    <t>Verify ESS user is able to add Multiple Dependants</t>
+  </si>
+  <si>
+    <t>Successful saved
+Details should be appeared under Dependants table</t>
+  </si>
+  <si>
+    <t>Successful saved
+Multiple details should be appeared under Dependants table</t>
+  </si>
+  <si>
+    <t>Successful deleted
+Entries should disappear from Dependants table</t>
+  </si>
+  <si>
+    <t>ESS user can add multiple entries of Immigration information</t>
+  </si>
+  <si>
+    <t>Verify ESS user is able to add Immigration Information information</t>
+  </si>
+  <si>
+    <t>Verify ESS user is able to add mulltiple entries of Immigration information</t>
+  </si>
+  <si>
+    <t>Successful uploading the file</t>
+  </si>
+  <si>
+    <t>Successful saved
+Details should be appeared under Immigration table</t>
+  </si>
+  <si>
+    <t>Successful saved
+Multiple details should be appeared under Immigration table</t>
+  </si>
+  <si>
+    <t>Verify ESS user is able to delete Immigration details</t>
+  </si>
+  <si>
+    <t>Successful deleted
+Entries should disappear from Immigration table</t>
+  </si>
+  <si>
+    <t>Verify ESS User is able to attach documents under Immigration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESS User can attach documents under Demandants </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify ESS User is able to attach documents under Demandants </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESS User can attach documents under Immigration </t>
+  </si>
+  <si>
+    <t>Verify ESS user cannot make changes on Job details</t>
+  </si>
+  <si>
+    <t>ESS user is restricted from editing the Salary fields</t>
+  </si>
+  <si>
+    <t>ESS user can only view the list of Supervisors</t>
+  </si>
+  <si>
+    <t>Verify ESS user is able to view list of Supervisors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User should be able to view list of Assigned Supervisors </t>
+  </si>
+  <si>
+    <t>TC_MyInfo_048</t>
+  </si>
+  <si>
+    <t>ESS user is restricted from editing the Report To fields</t>
+  </si>
+  <si>
+    <t>Verify ESS user cannot edit restricted fields on Report To</t>
+  </si>
+  <si>
+    <t>Successful saved
+Details should be appeared under Work Experience table</t>
+  </si>
+  <si>
+    <t>Verify ESS user is able to add multiple Work Experience</t>
+  </si>
+  <si>
+    <t>Verify ESS user is able to add Work Experience</t>
+  </si>
+  <si>
+    <t>Successful saved
+Multiple details should be appeared under Work Experience table</t>
+  </si>
+  <si>
+    <t>Verify ESS user is able to delete Work Experience</t>
+  </si>
+  <si>
+    <t>Successful deleted
+Entries should disappear from Work Experience table</t>
+  </si>
+  <si>
+    <t>Verify ESS user is able to add Education details</t>
+  </si>
+  <si>
+    <t>Verify ESS user is able to add multiple Education details</t>
+  </si>
+  <si>
+    <t>Verify ESS user is able to delete Education details</t>
+  </si>
+  <si>
+    <t>Successful saved
+Details should be appeared under Education table</t>
+  </si>
+  <si>
+    <t>Successful saved
+Multiple details should be appeared under Education table</t>
+  </si>
+  <si>
+    <t>Successful deleted
+Entries should disappear from Education table</t>
+  </si>
+  <si>
+    <t>Verify ESS user is able to add Skills details</t>
+  </si>
+  <si>
+    <t>Successful saved
+Details should be appeared under Skills table</t>
+  </si>
+  <si>
+    <t>Verify ESS user is able to add multiple Skills details</t>
+  </si>
+  <si>
+    <t>Successful saved
+Multiple details should be appeared under Skills table</t>
+  </si>
+  <si>
+    <t>Verify ESS user is able to delete Skills details</t>
+  </si>
+  <si>
+    <t>Successful deleted
+Entries should disappear from Skills table</t>
+  </si>
+  <si>
+    <t>Verify ESS user is able to add Languages details</t>
+  </si>
+  <si>
+    <t>Successful saved
+Details should be appeared under Language table</t>
+  </si>
+  <si>
+    <t>Verify ESS user is able to add multiple Language details</t>
+  </si>
+  <si>
+    <t>Successful saved
+Multiple details should be appeared under Language table</t>
+  </si>
+  <si>
+    <t>Verify ESS user is able to delete Languages details</t>
+  </si>
+  <si>
+    <t>Successful deleted
+Entries should disappear from Languages table</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESS user can upload attachments </t>
+  </si>
+  <si>
+    <t>Verify ESS user is able to add License details</t>
+  </si>
+  <si>
+    <t>Successful saved
+Details should be appeared under License table</t>
+  </si>
+  <si>
+    <t>Verify ESS user is able to add multiple License details</t>
+  </si>
+  <si>
+    <t>Successful saved
+Multiple details should be appeared under License table</t>
+  </si>
+  <si>
+    <t>Verify ESS user is able to delete License details</t>
+  </si>
+  <si>
+    <t>Successful deleted
+Entries should disappear from License table</t>
+  </si>
+  <si>
+    <t>ESS user can delete attachments</t>
+  </si>
+  <si>
+    <t>Verify ESS user is able to delete Memberships</t>
+  </si>
+  <si>
+    <t>Doc, Xls and PDF Document</t>
+  </si>
+  <si>
+    <t>Successful saved
+Details should be appeared under Membership table</t>
+  </si>
+  <si>
+    <t>Successful deleted
+Entries should disappear from Membership table</t>
+  </si>
+  <si>
+    <t>ESS can upload attachments under Membership records</t>
+  </si>
+  <si>
+    <t>Comments</t>
+  </si>
+  <si>
+    <t>Project Name</t>
+  </si>
+  <si>
+    <t>Orange HRM</t>
+  </si>
+  <si>
+    <t>Module</t>
+  </si>
+  <si>
+    <t>MyInfo</t>
+  </si>
+  <si>
+    <t>Prepared By</t>
+  </si>
+  <si>
+    <t>Version No</t>
+  </si>
+  <si>
+    <t>V1. 0</t>
+  </si>
+  <si>
+    <t>Initial Draft</t>
+  </si>
+  <si>
+    <t>Review By</t>
+  </si>
+  <si>
+    <t>Approved By</t>
+  </si>
+  <si>
+    <t>Name of Product Manager</t>
+  </si>
+  <si>
+    <t>Names of Product Manager 
+Developer 
+QA Team</t>
+  </si>
+  <si>
+    <t>Test Cases</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>TC_MyInfo_008.1</t>
+  </si>
+  <si>
+    <t>TC_MyInfo_008.2</t>
+  </si>
+  <si>
+    <t>TC_MyInfo_008.3</t>
+  </si>
+  <si>
+    <t>TC_MyInfo_008.4</t>
+  </si>
+  <si>
+    <t>TC_MyInfo_008.5</t>
+  </si>
+  <si>
+    <t>TC_MyInfo_008.6</t>
+  </si>
+  <si>
+    <t>TC_MyInfo_008.7</t>
+  </si>
+  <si>
+    <t>TC_MyInfo_008.8</t>
+  </si>
+  <si>
+    <t>TC_MyInfo_008.9</t>
+  </si>
+  <si>
+    <t>TC_MyInfo_008.10</t>
+  </si>
+  <si>
+    <t>TC_MyInfo_008.11</t>
+  </si>
+  <si>
+    <t>TC_MyInfo_008.12</t>
+  </si>
+  <si>
+    <t>Image 1MB</t>
+  </si>
+  <si>
+    <t>Image &lt; 1MB</t>
+  </si>
+  <si>
+    <t>Image &gt; 1MB</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Successful upload
+Picture should be uploaded adding image JPG 1MB</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Successful upload
+Picture should be uploaded adding image JPG &lt; 1MB</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Successful upload
+Picture should be uploaded adding image PNG 1MB</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Successful upload
+Picture should be uploaded adding image PNG &lt; 1MB</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Successful upload
+Picture should be uploaded adding image Gif 1MB</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Successful upload
+Picture should be uploaded adding image Gif &lt; 1MB</t>
+  </si>
+  <si>
+    <t>TC_MyInfo_042.1</t>
+  </si>
+  <si>
+    <t>TC_MyInfo_042.2</t>
+  </si>
+  <si>
+    <t>TC_MyInfo_042.3</t>
+  </si>
+  <si>
+    <t>TC_MyInfo_042.4</t>
+  </si>
+  <si>
+    <t>TC_MyInfo_042.5</t>
+  </si>
+  <si>
+    <t>TC_MyInfo_042.6</t>
+  </si>
+  <si>
+    <t>TC_MyInfo_042.7</t>
+  </si>
+  <si>
+    <t>TC_MyInfo_042.8</t>
+  </si>
+  <si>
+    <t>TC_MyInfo_042.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESS user can add a photograph </t>
+  </si>
+  <si>
+    <t>PDF Document &lt;1MB</t>
+  </si>
+  <si>
+    <t>PDF Document 1MB</t>
+  </si>
+  <si>
+    <t>PDF Document &gt; 1MB</t>
+  </si>
+  <si>
+    <t>Unsuccessful upload
+Display error message "Validation failed" in the screen</t>
+  </si>
+  <si>
+    <t>Itumeleng Sekati</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Username: Admin 
+Password: admin123</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Username: Admin 
+Password: administration123 </t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Username: Adminnistration 
+Password: admin123</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Username: Administration 
+Password: administration123</t>
+  </si>
+  <si>
+    <t>1. Login to Orange HRM as ESS user
 2.Click on MyInfo tab
-3.Click on Peronal Details link</t>
-  </si>
-  <si>
-    <t>Verify ESS user can edit Personal Details</t>
-  </si>
-  <si>
-    <t>User should be able to view Personal Details</t>
-  </si>
-  <si>
-    <t>Verify ESS user cannot edit restricted fields</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Login to Orange HM as ESS user
+3.Click on Personal Details link</t>
+  </si>
+  <si>
+    <t>1. Login to Orange HRM as ESS user
 2.Click on MyInfo tab
-3.Click on Peronal Details link
+3.Click on Personal Details link
+4.Click on edit button
+5.Edit FullName/Middle Name, Last Name, License, Expiry Date, Gender, Marital Status and Nationality
+6. Click Save button</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Login to Orange HRM as ESS user
+2.Click on MyInfo tab
+3.Click on Personal Details link
 4.Click on edit button
 </t>
   </si>
   <si>
-    <t>The fileds should be not-editable 
+    <t>The Flields should be not-editable 
 Employee ID
 SSN No
 SIN No
@@ -357,27 +899,10 @@
 Date of Birth</t>
   </si>
   <si>
-    <t>1. Login to Orange HM as ESS user
-2.Click on MyInfo tab
-3.Click on Peronal Details link
-4.Click on edit button
-5.Edit FullName/Middle Name, Last Name, License, Expiry Date, Gender, Marital Status and Nationality
-6. Click Save button</t>
-  </si>
-  <si>
-    <t>TC_MyInfo_012</t>
-  </si>
-  <si>
-    <t>TC_MyInfo_013</t>
-  </si>
-  <si>
-    <t>TC_MyInfo_014</t>
-  </si>
-  <si>
-    <t>TC_MyInfo_015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Login to Orange HM as ESS user
+    <t>Verify ESS user is able to add JPG Photography</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Login to Orange HRM as ESS user
 2.Click on MyInfo tab
 3.Click on the photograph at corner of the screen
 4.Click "Browse" and then select a photograph the relevant path
@@ -385,22 +910,22 @@
 </t>
   </si>
   <si>
-    <t>Verify ESS is able to view Contacts Details</t>
-  </si>
-  <si>
-    <t>Verify ESS is able to edit Contacts Details</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Login to Orange HM as ESS user
+    <t>Verify ESS user is able to add Photography PNG</t>
+  </si>
+  <si>
+    <t>Verify ESS user is able to add Photography Gif</t>
+  </si>
+  <si>
+    <t>Verify ESS user is able to add Photography Exe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Login to Orange HRM as ESS user
 2.Click on MyInfo tab
 3.Click on Contacts Details link
 </t>
   </si>
   <si>
-    <t>User should able to view Contact Details</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Login to Orange HM as ESS user
+    <t xml:space="preserve">1. Login to Orange HRM as ESS user
 2.Click on MyInfo tab
 3.Click on Contacts Details link
 4.Click Edit button
@@ -409,113 +934,7 @@
 </t>
   </si>
   <si>
-    <t>User should be able to edit and save Contact Details</t>
-  </si>
-  <si>
-    <t>TC_MyInfo_016</t>
-  </si>
-  <si>
-    <t>TC_MyInfo_017</t>
-  </si>
-  <si>
-    <t>TC_MyInfo_018</t>
-  </si>
-  <si>
-    <t>TC_MyInfo_019</t>
-  </si>
-  <si>
-    <t>TC_MyInfo_020</t>
-  </si>
-  <si>
-    <t>TC_MyInfo_021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify ESS user is able to add Emergency Contact </t>
-  </si>
-  <si>
-    <t>TC_MyInfo_022</t>
-  </si>
-  <si>
-    <t>TC_MyInfo_023</t>
-  </si>
-  <si>
-    <t>TC_MyInfo_024</t>
-  </si>
-  <si>
-    <t>TC_MyInfo_025</t>
-  </si>
-  <si>
-    <t>TC_MyInfo_026</t>
-  </si>
-  <si>
-    <t>TC_MyInfo_027</t>
-  </si>
-  <si>
-    <t>TC_MyInfo_028</t>
-  </si>
-  <si>
-    <t>TC_MyInfo_029</t>
-  </si>
-  <si>
-    <t>TC_MyInfo_030</t>
-  </si>
-  <si>
-    <t>TC_MyInfo_031</t>
-  </si>
-  <si>
-    <t>TC_MyInfo_032</t>
-  </si>
-  <si>
-    <t>TC_MyInfo_033</t>
-  </si>
-  <si>
-    <t>TC_MyInfo_034</t>
-  </si>
-  <si>
-    <t>TC_MyInfo_035</t>
-  </si>
-  <si>
-    <t>TC_MyInfo_036</t>
-  </si>
-  <si>
-    <t>TC_MyInfo_037</t>
-  </si>
-  <si>
-    <t>TC_MyInfo_038</t>
-  </si>
-  <si>
-    <t>TC_MyInfo_039</t>
-  </si>
-  <si>
-    <t>TC_MyInfo_040</t>
-  </si>
-  <si>
-    <t>TC_MyInfo_041</t>
-  </si>
-  <si>
-    <t>TC_MyInfo_043</t>
-  </si>
-  <si>
-    <t>TC_MyInfo_044</t>
-  </si>
-  <si>
-    <t>TC_MyInfo_045</t>
-  </si>
-  <si>
-    <t>TC_MyInfo_046</t>
-  </si>
-  <si>
-    <t>Successful saved
-Details should be appeared under Emergency Contact table</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify ESS user is able to delete Emergency Contact </t>
-  </si>
-  <si>
-    <t>Verify ESS user is able to add Multiple Emergency Contacts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Login to Orange HM as ESS user
+    <t xml:space="preserve">1. Login to Orange HRM as ESS user
 2.Click on MyInfo tab
 3.Click on Emergency Contact link
 4.Click Add button
@@ -524,11 +943,7 @@
 </t>
   </si>
   <si>
-    <t>Successful saved
-Multiple details should be appeared under Emergency Contact table</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Login to Orange HM as ESS user
+    <t xml:space="preserve">1. Login to Orange HRM as ESS user
 2.Click on MyInfo tab
 3.Click on Emergency Contact link
 4.Click on the check box next to particular entry
@@ -536,41 +951,16 @@
 </t>
   </si>
   <si>
-    <t>Successful deleted
-Entries should disappear from Emergency Contacts table</t>
-  </si>
-  <si>
-    <t>Verify ESS user is able to delete Dependants</t>
-  </si>
-  <si>
-    <t>ESS User can attach documents under Emergency Contact</t>
-  </si>
-  <si>
-    <t>ESS User can attach documents under Demandant</t>
-  </si>
-  <si>
-    <t>ESS user can add multiple Dependants</t>
-  </si>
-  <si>
-    <t>ESS user can add Dependants</t>
-  </si>
-  <si>
-    <t>Verify ESS User is able to attach documents under Emergency Contact</t>
-  </si>
-  <si>
-    <t>Successful upload file</t>
-  </si>
-  <si>
-    <t>TC_MyInfo_047</t>
-  </si>
-  <si>
-    <t>Verify ESS user is able to add Dependants</t>
-  </si>
-  <si>
-    <t>Verify ESS user is able to add Multiple Dependants</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Login to Orange HM as ESS user
+    <t xml:space="preserve">1. Login to Orange HRM as ESS user
+2.Click on MyInfo tab
+3.Click on Emergency Contact link
+4.Click Add button under the “AttacHRMent” 
+5.Select a file from a relevant path 
+6.Click Upload button
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Login to Orange HRM as ESS user
 2.Click on MyInfo tab
 3.Click on Dependants link
 4.Click Add button
@@ -579,7 +969,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">1. Login to Orange HM as ESS user
+    <t xml:space="preserve">1. Login to Orange HRM as ESS user
 2.Click on MyInfo tab
 3.Click on Dependants link
 4.Click on the check box next to particular entry
@@ -587,42 +977,16 @@
 </t>
   </si>
   <si>
-    <t>Successful saved
-Details should be appeared under Dependants table</t>
-  </si>
-  <si>
-    <t>Successful saved
-Multiple details should be appeared under Dependants table</t>
-  </si>
-  <si>
-    <t>Successful deleted
-Entries should disappear from Dependants table</t>
-  </si>
-  <si>
-    <t>ESS user can add multiple entries of Immigration information</t>
-  </si>
-  <si>
-    <t>Verify ESS user is able to add Immigration Information information</t>
-  </si>
-  <si>
-    <t>Verify ESS user is able to add mulltiple entries of Immigration information</t>
-  </si>
-  <si>
-    <t>Successful uploading the file</t>
-  </si>
-  <si>
-    <t>Successful saved
-Details should be appeared under Immigration table</t>
-  </si>
-  <si>
-    <t>Successful saved
-Multiple details should be appeared under Immigration table</t>
-  </si>
-  <si>
-    <t>Verify ESS user is able to delete Immigration details</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Login to Orange HM as ESS user
+    <t xml:space="preserve">1. Login to Orange HRM as ESS user
+2.Click on MyInfo tab
+3.Click on Demandants link
+4.Click Add button under the “AttacHRMent” 
+5.Select a file from a relevant path 
+6.Click Upload button
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Login to Orange HRM as ESS user
 2.Click on MyInfo tab
 3.Click on Immigration link
 4.Click Add button
@@ -631,11 +995,7 @@
 </t>
   </si>
   <si>
-    <t>Successful deleted
-Entries should disappear from Immigration table</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Login to Orange HM as ESS user
+    <t xml:space="preserve">1. Login to Orange HRM as ESS user
 2.Click on MyInfo tab
 3.Click on Immigration link
 4.Click Add button
@@ -645,7 +1005,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">1. Login to Orange HM as ESS user
+    <t xml:space="preserve">1. Login to Orange HRM as ESS user
 2.Click on MyInfo tab
 3.Click on Immigration link
 4.Click on the check box next to particular entry
@@ -653,26 +1013,23 @@
 </t>
   </si>
   <si>
-    <t>Verify ESS User is able to attach documents under Immigration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESS User can attach documents under Demandants </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify ESS User is able to attach documents under Demandants </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESS User can attach documents under Immigration </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Login to Orange HM as ESS user
+    <t xml:space="preserve">1. Login to Orange HRM as ESS user
+2.Click on MyInfo tab
+3.Click on Immigration link
+4.Click Add button under the “AttacHRMent” 
+5.Select a file from a relevant path 
+6.Click Upload button
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Login to Orange HRM as ESS user
 2.Click on MyInfo tab
 3.Click on Job link
 4.Click on fields Job Tittle, Employment Status, Job Category, Joined Day, Sub Unit, Location, Start Date, End Date
 </t>
   </si>
   <si>
-    <t>The fileds should be not-editable 
+    <t>The Flields should be not-editable 
 Job Tittle
 Employment Status
 Job Category
@@ -683,87 +1040,46 @@
 End Date</t>
   </si>
   <si>
-    <t>Verify ESS user cannot edit restricted fields on Salary fileds</t>
-  </si>
-  <si>
-    <t>Verify ESS user cannot make changes on Job details</t>
-  </si>
-  <si>
-    <t>ESS user is restricted from editing the Salary fields</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Login to Orange HM as ESS user
+    <t>Verify ESS user cannot edit restricted fields on Salary Flields</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Login to Orange HRM as ESS user
 2.Click on MyInfo tab
 3.Click on Salary link
-4.Click on fields Salary Component, Pay Frecuency, Currency, Amount, Comments, Direct Deposit Details, Attachments
+4.Click on fields Salary Component, Pay Frecuency, Currency, Amount, Comments, Direct Deposit Details, AttacHRMents
 </t>
   </si>
   <si>
-    <t>The fileds should be not-editable 
+    <t>The Flields should be not-editable 
 Salary Component
 Pay Frecuency
-Curreny
+Currency
 Amount
 Components
 Direct Deposit Details
-Attchments</t>
-  </si>
-  <si>
-    <t>ESS user can only view the list of Supervisors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Login to Orange HM as ESS user
+AttcHRMents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Login to Orange HRM as ESS user
 2.Click on MyInfo tab
 3.Click on Report To link
 </t>
   </si>
   <si>
-    <t>Verify ESS user is able to view list of Supervisors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">User should be able to view list of Assigned Supervisors </t>
-  </si>
-  <si>
-    <t>TC_MyInfo_048</t>
-  </si>
-  <si>
-    <t>ESS user is restricted from editing the Report To fields</t>
-  </si>
-  <si>
-    <t>Verify ESS user cannot edit restricted fields on Report To</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Login to Orange HM as ESS user
+    <t xml:space="preserve">1. Login to Orange HRM as ESS user
 2.Click on MyInfo tab
 3.Click on Report To link
-4.Click on fields Assigned supervisors, Assigned subordinates, Attachments
+4.Click on fields Assigned supervisors, Assigned subordinates, AttacHRMents
 </t>
   </si>
   <si>
     <t>The fields Should be not-editable
 Assigned supervisors
 Assigned subordinates
-Attachments</t>
-  </si>
-  <si>
-    <t>Successful saved
-Details should be appeared under Work Experience table</t>
-  </si>
-  <si>
-    <t>Verify ESS user is able to add multiple Work Experience</t>
-  </si>
-  <si>
-    <t>Verify ESS user is able to add Work Experience</t>
-  </si>
-  <si>
-    <t>Successful saved
-Multiple details should be appeared under Work Experience table</t>
-  </si>
-  <si>
-    <t>Verify ESS user is able to delete Work Experience</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Login to Orange HM as ESS user
+AttacHRMents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Login to Orange HRM as ESS user
 2.Click on MyInfo tab
 3.Click on Qualifications link
 4.Click add button under Work Experience
@@ -772,7 +1088,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">1. Login to Orange HM as ESS user
+    <t xml:space="preserve">1. Login to Orange HRM as ESS user
 2.Click on MyInfo tab
 3.Click on Qualification link
 4.Click on the check box next to particular entry in Work Experience
@@ -780,20 +1096,7 @@
 </t>
   </si>
   <si>
-    <t>Successful deleted
-Entries should disappear from Work Experience table</t>
-  </si>
-  <si>
-    <t>Verify ESS user is able to add Education details</t>
-  </si>
-  <si>
-    <t>Verify ESS user is able to add multiple Education details</t>
-  </si>
-  <si>
-    <t>Verify ESS user is able to delete Education details</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Login to Orange HM as ESS user
+    <t xml:space="preserve">1. Login to Orange HRM as ESS user
 2.Click on MyInfo tab
 3.Click on Qualifications link
 4.Click add button under Education
@@ -802,19 +1105,7 @@
 </t>
   </si>
   <si>
-    <t>Successful saved
-Details should be appeared under Education table</t>
-  </si>
-  <si>
-    <t>Successful saved
-Multiple details should be appeared under Education table</t>
-  </si>
-  <si>
-    <t>Successful deleted
-Entries should disappear from Education table</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Login to Orange HM as ESS user
+    <t xml:space="preserve">1. Login to Orange HRM as ESS user
 2.Click on MyInfo tab
 3.Click on Qualifications link
 4.Click on the check box next to particular entry in Education
@@ -822,10 +1113,7 @@
 </t>
   </si>
   <si>
-    <t>Verify ESS user is able to add Skills details</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Login to Orange HM as ESS user
+    <t xml:space="preserve">1. Login to Orange HRM as ESS user
 2.Click on MyInfo tab
 3.Click on Qualifications link
 4.Click add button under Skills
@@ -834,21 +1122,7 @@
 </t>
   </si>
   <si>
-    <t>Successful saved
-Details should be appeared under Skills table</t>
-  </si>
-  <si>
-    <t>Verify ESS user is able to add multiple Skills details</t>
-  </si>
-  <si>
-    <t>Successful saved
-Multiple details should be appeared under Skills table</t>
-  </si>
-  <si>
-    <t>Verify ESS user is able to delete Skills details</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Login to Orange HM as ESS user
+    <t xml:space="preserve">1. Login to Orange HRM as ESS user
 2.Click on MyInfo tab
 3.Click on Qualifications link
 4.Click on the check box next to particular entry in Skills
@@ -856,14 +1130,7 @@
 </t>
   </si>
   <si>
-    <t>Successful deleted
-Entries should disappear from Skills table</t>
-  </si>
-  <si>
-    <t>Verify ESS user is able to add Languages details</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Login to Orange HM as ESS user
+    <t xml:space="preserve">1. Login to Orange HRM as ESS user
 2.Click on MyInfo tab
 3.Click on Qualifications link
 4.Click add button under Languages
@@ -872,21 +1139,7 @@
 </t>
   </si>
   <si>
-    <t>Successful saved
-Details should be appeared under Language table</t>
-  </si>
-  <si>
-    <t>Verify ESS user is able to add multiple Language details</t>
-  </si>
-  <si>
-    <t>Successful saved
-Multiple details should be appeared under Language table</t>
-  </si>
-  <si>
-    <t>Verify ESS user is able to delete Languages details</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Login to Orange HM as ESS user
+    <t xml:space="preserve">1. Login to Orange HRM as ESS user
 2.Click on MyInfo tab
 3.Click on Qualifications link
 4.Click on the check box next to particular entry in Languages
@@ -894,17 +1147,7 @@
 </t>
   </si>
   <si>
-    <t>Successful deleted
-Entries should disappear from Languages table</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESS user can upload attachments </t>
-  </si>
-  <si>
-    <t>Verify ESS user is able to add License details</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Login to Orange HM as ESS user
+    <t xml:space="preserve">1. Login to Orange HRM as ESS user
 2.Click on MyInfo tab
 3.Click on Qualifications link
 4.Click add button under License
@@ -913,21 +1156,7 @@
 </t>
   </si>
   <si>
-    <t>Successful saved
-Details should be appeared under License table</t>
-  </si>
-  <si>
-    <t>Verify ESS user is able to add multiple License details</t>
-  </si>
-  <si>
-    <t>Successful saved
-Multiple details should be appeared under License table</t>
-  </si>
-  <si>
-    <t>Verify ESS user is able to delete License details</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Login to Orange HM as ESS user
+    <t xml:space="preserve">1. Login to Orange HRM as ESS user
 2.Click on MyInfo tab
 3.Click on Qualifications link
 4.Click on the check box next to particular entry in License
@@ -935,57 +1164,71 @@
 </t>
   </si>
   <si>
-    <t>Successful deleted
-Entries should disappear from License table</t>
-  </si>
-  <si>
-    <t>Verify ESS user is able to upload multiple attachments</t>
-  </si>
-  <si>
-    <t>Verify ESS user is able to delete attachments</t>
-  </si>
-  <si>
-    <t>ESS user can delete attachments</t>
-  </si>
-  <si>
-    <t>Verify ESS user is able to add Memebership details</t>
-  </si>
-  <si>
-    <t>Verify ESS user is able to add multiple Memebership details</t>
-  </si>
-  <si>
-    <t>Verify ESS user is able to delete Memberships</t>
-  </si>
-  <si>
-    <t>Verify ESS user is able to upload attachment</t>
-  </si>
-  <si>
-    <t>Doc, Xls and PDF Document</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Login to Orange HM as ESS user
+    <t xml:space="preserve">ESS user can upload attacHRMent </t>
+  </si>
+  <si>
+    <t>Verify ESS user is able to upload attacHRMent PDF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Login to Orange HRM as ESS user
 2.Click on MyInfo tab
 3.Click on Qualifications link
-4.Click on the check box next to particular entry in attachments
-5.Click on delete button
-</t>
-  </si>
-  <si>
-    <t>Successful deleted
-Entries should disappear from attachment table</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Login to Orange HM as ESS user
-2.Click on MyInfo tab
-3.Click on Qualifications link
-4.Click add button under Attachment
+4.Click add button under AttacHRMent
 5.Click “Browse” and select the file from the relevant path 
 6.Enter comment if required
 7.Click Upload button
 </t>
   </si>
   <si>
-    <t xml:space="preserve">1. Login to Orange HM as ESS user
+    <t>Successful uploaded
+ AttacHRMents should be appeared under attacHRMent table</t>
+  </si>
+  <si>
+    <t>Verify ESS user is able to upload attacHRMent</t>
+  </si>
+  <si>
+    <t>ESS user can upload multiple attcHRMents</t>
+  </si>
+  <si>
+    <t>Verify ESS user is able to upload multiple attacHRMents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Login to Orange HRM as ESS user
+2.Click on MyInfo tab
+3.Click on Qualifications link
+4.Click add button under AttacHRMents
+5.Click “Browse” and select the file from the relevant path 
+6.Enter comment if required
+7.Click Upload button
+</t>
+  </si>
+  <si>
+    <t>Successful uploaded
+Multiple attacHRMents should be appeared under attacHRMent table</t>
+  </si>
+  <si>
+    <t>ESS user can delete attacHRMents</t>
+  </si>
+  <si>
+    <t>Verify ESS user is able to delete attacHRMents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Login to Orange HRM as ESS user
+2.Click on MyInfo tab
+3.Click on Qualifications link
+4.Click on the check box next to particular entry in attacHRMents
+5.Click on delete button
+</t>
+  </si>
+  <si>
+    <t>Successful deleted
+Entries should disappear from attacHRMent table</t>
+  </si>
+  <si>
+    <t>Verify ESS user is able to add Membership details</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Login to Orange HRM as ESS user
 2.Click on MyInfo tab
 3.Click on Membership link
 4.Click add button 
@@ -994,19 +1237,14 @@
 </t>
   </si>
   <si>
-    <t>Successful saved
-Details should be appeared under Membership table</t>
+    <t>Verify ESS user is able to add multiple Membership details</t>
   </si>
   <si>
     <t>Successful uploaded
-Multiple attchments should be appeared under Membership table</t>
-  </si>
-  <si>
-    <t>Successful deleted
-Entries should disappear from Membership table</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Login to Orange HM as ESS user
+Multiple attcHRMents should be appeared under Membership table</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Login to Orange HRM as ESS user
 2.Click on MyInfo tab
 3.Click on Membership link
 4.Click on the check box next to particular entry
@@ -1014,253 +1252,22 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">1. Login to Orange HM as ESS user
+    <t>ESS can upload attacHRMents under Membership records</t>
+  </si>
+  <si>
+    <t>Verify ESS user is able to upload attacHRMents under Membership records</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Login to Orange HRM as ESS user
 2.Click on MyInfo tab
 3.Click on Membership link
-4.Click Add button under the “Attachment” 
+4.Click Add button under the “AttacHRMent” 
 5.Select a file from a relevant path 
 6.Click Upload button
 </t>
   </si>
   <si>
-    <t xml:space="preserve">1. Login to Orange HM as ESS user
-2.Click on MyInfo tab
-3.Click on Immigration link
-4.Click Add button under the “Attachment” 
-5.Select a file from a relevant path 
-6.Click Upload button
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Login to Orange HM as ESS user
-2.Click on MyInfo tab
-3.Click on Demandants link
-4.Click Add button under the “Attachment” 
-5.Select a file from a relevant path 
-6.Click Upload button
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Login to Orange HM as ESS user
-2.Click on MyInfo tab
-3.Click on Emergency Contact link
-4.Click Add button under the “Attachment” 
-5.Select a file from a relevant path 
-6.Click Upload button
-</t>
-  </si>
-  <si>
-    <t>ESS can upload attachments under Membership records</t>
-  </si>
-  <si>
-    <t>Verify ESS user is able to upload attachments under Membership records</t>
-  </si>
-  <si>
-    <t>Comments</t>
-  </si>
-  <si>
-    <t>Project Name</t>
-  </si>
-  <si>
-    <t>Orange HRM</t>
-  </si>
-  <si>
-    <t>Module</t>
-  </si>
-  <si>
-    <t>MyInfo</t>
-  </si>
-  <si>
-    <t>Prepared By</t>
-  </si>
-  <si>
-    <t>Version No</t>
-  </si>
-  <si>
-    <t>V1. 0</t>
-  </si>
-  <si>
-    <t>Initial Draft</t>
-  </si>
-  <si>
-    <t>V1.1</t>
-  </si>
-  <si>
-    <t>V1.2</t>
-  </si>
-  <si>
-    <t>You need to add some test cases, updated few test cases according inputs provided by team</t>
-  </si>
-  <si>
-    <t>Review By</t>
-  </si>
-  <si>
-    <t>Approved By</t>
-  </si>
-  <si>
-    <t>Name of Product Manager</t>
-  </si>
-  <si>
-    <t>Names of Product Manager 
-Developer 
-QA Team</t>
-  </si>
-  <si>
-    <t>Test Cases</t>
-  </si>
-  <si>
-    <t>x</t>
-  </si>
-  <si>
-    <t>TC_MyInfo_008.1</t>
-  </si>
-  <si>
-    <t>TC_MyInfo_008.2</t>
-  </si>
-  <si>
-    <t>TC_MyInfo_008.3</t>
-  </si>
-  <si>
-    <t>TC_MyInfo_008.4</t>
-  </si>
-  <si>
-    <t>TC_MyInfo_008.5</t>
-  </si>
-  <si>
-    <t>TC_MyInfo_008.6</t>
-  </si>
-  <si>
-    <t>TC_MyInfo_008.7</t>
-  </si>
-  <si>
-    <t>TC_MyInfo_008.8</t>
-  </si>
-  <si>
-    <t>TC_MyInfo_008.9</t>
-  </si>
-  <si>
-    <t>TC_MyInfo_008.10</t>
-  </si>
-  <si>
-    <t>TC_MyInfo_008.11</t>
-  </si>
-  <si>
-    <t>TC_MyInfo_008.12</t>
-  </si>
-  <si>
-    <t>Image 1MB</t>
-  </si>
-  <si>
-    <t>Image &lt; 1MB</t>
-  </si>
-  <si>
-    <t>Image &gt; 1MB</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Successful upload
-Picture should be uploaded adding image JPG 1MB</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Successful upload
-Picture should be uploaded adding image JPG &lt; 1MB</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Successful upload
-Picture should be uploaded adding image PNG 1MB</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Successful upload
-Picture should be uploaded adding image PNG &lt; 1MB</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Successful upload
-Picture should be uploaded adding image Gif 1MB</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Successful upload
-Picture should be uploaded adding image Gif &lt; 1MB</t>
-  </si>
-  <si>
-    <t>TC_MyInfo_042.1</t>
-  </si>
-  <si>
-    <t>TC_MyInfo_042.2</t>
-  </si>
-  <si>
-    <t>TC_MyInfo_042.3</t>
-  </si>
-  <si>
-    <t>TC_MyInfo_042.4</t>
-  </si>
-  <si>
-    <t>TC_MyInfo_042.5</t>
-  </si>
-  <si>
-    <t>TC_MyInfo_042.6</t>
-  </si>
-  <si>
-    <t>TC_MyInfo_042.7</t>
-  </si>
-  <si>
-    <t>TC_MyInfo_042.8</t>
-  </si>
-  <si>
-    <t>TC_MyInfo_042.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESS user can upload attachment </t>
-  </si>
-  <si>
-    <t>Verify ESS user is able to upload attachment PDF</t>
-  </si>
-  <si>
-    <t>Verify ESS user is able to add JPG photografy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESS user can add a photograph </t>
-  </si>
-  <si>
-    <t>Verify ESS user is able to add photografy PNG</t>
-  </si>
-  <si>
-    <t>Verify ESS user is able to add photografy Gif</t>
-  </si>
-  <si>
-    <t>Verify ESS user is able to add photografy Exe</t>
-  </si>
-  <si>
-    <t>PDF Document &lt;1MB</t>
-  </si>
-  <si>
-    <t>PDF Document 1MB</t>
-  </si>
-  <si>
-    <t>PDF Document &gt; 1MB</t>
-  </si>
-  <si>
-    <t>Successful uploaded
- Attachments should be appeared under attachment table</t>
-  </si>
-  <si>
-    <t>Successful uploaded
-Multiple attachments should be appeared under attachment table</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Login to Orange HM as ESS user
-2.Click on MyInfo tab
-3.Click on Qualifications link
-4.Click add button under Attachments
-5.Click “Browse” and select the file from the relevant path 
-6.Enter comment if required
-7.Click Upload button
-</t>
-  </si>
-  <si>
-    <t>Unsuccessful upload
-Display error message "Validation failed" in the screen</t>
-  </si>
-  <si>
-    <t>Itumeleng Sekati</t>
+    <t>ESS User can attach documents under Dependants</t>
   </si>
 </sst>
 </file>
@@ -1646,7 +1653,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1826,6 +1833,9 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1857,8 +1867,8 @@
         <xdr:to>
           <xdr:col>10</xdr:col>
           <xdr:colOff>2971800</xdr:colOff>
-          <xdr:row>8</xdr:row>
-          <xdr:rowOff>1438275</xdr:rowOff>
+          <xdr:row>9</xdr:row>
+          <xdr:rowOff>3175</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -1912,8 +1922,8 @@
         <xdr:to>
           <xdr:col>10</xdr:col>
           <xdr:colOff>2971800</xdr:colOff>
-          <xdr:row>9</xdr:row>
-          <xdr:rowOff>1400175</xdr:rowOff>
+          <xdr:row>10</xdr:row>
+          <xdr:rowOff>3175</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -1967,8 +1977,8 @@
         <xdr:to>
           <xdr:col>10</xdr:col>
           <xdr:colOff>2971800</xdr:colOff>
-          <xdr:row>10</xdr:row>
-          <xdr:rowOff>1438275</xdr:rowOff>
+          <xdr:row>11</xdr:row>
+          <xdr:rowOff>3175</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2022,8 +2032,8 @@
         <xdr:to>
           <xdr:col>10</xdr:col>
           <xdr:colOff>2971800</xdr:colOff>
-          <xdr:row>11</xdr:row>
-          <xdr:rowOff>1476375</xdr:rowOff>
+          <xdr:row>12</xdr:row>
+          <xdr:rowOff>3175</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2077,8 +2087,8 @@
         <xdr:to>
           <xdr:col>10</xdr:col>
           <xdr:colOff>2971800</xdr:colOff>
-          <xdr:row>12</xdr:row>
-          <xdr:rowOff>1419225</xdr:rowOff>
+          <xdr:row>13</xdr:row>
+          <xdr:rowOff>3175</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2132,8 +2142,8 @@
         <xdr:to>
           <xdr:col>10</xdr:col>
           <xdr:colOff>2971800</xdr:colOff>
-          <xdr:row>13</xdr:row>
-          <xdr:rowOff>1571625</xdr:rowOff>
+          <xdr:row>14</xdr:row>
+          <xdr:rowOff>174625</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2187,8 +2197,8 @@
         <xdr:to>
           <xdr:col>10</xdr:col>
           <xdr:colOff>2971800</xdr:colOff>
-          <xdr:row>14</xdr:row>
-          <xdr:rowOff>1476375</xdr:rowOff>
+          <xdr:row>15</xdr:row>
+          <xdr:rowOff>3175</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2242,8 +2252,8 @@
         <xdr:to>
           <xdr:col>10</xdr:col>
           <xdr:colOff>2971800</xdr:colOff>
-          <xdr:row>15</xdr:row>
-          <xdr:rowOff>1476375</xdr:rowOff>
+          <xdr:row>16</xdr:row>
+          <xdr:rowOff>3175</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2297,8 +2307,8 @@
         <xdr:to>
           <xdr:col>10</xdr:col>
           <xdr:colOff>2971800</xdr:colOff>
-          <xdr:row>16</xdr:row>
-          <xdr:rowOff>1476375</xdr:rowOff>
+          <xdr:row>17</xdr:row>
+          <xdr:rowOff>3175</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2352,8 +2362,8 @@
         <xdr:to>
           <xdr:col>10</xdr:col>
           <xdr:colOff>2971800</xdr:colOff>
-          <xdr:row>17</xdr:row>
-          <xdr:rowOff>1400175</xdr:rowOff>
+          <xdr:row>18</xdr:row>
+          <xdr:rowOff>3175</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2407,8 +2417,8 @@
         <xdr:to>
           <xdr:col>10</xdr:col>
           <xdr:colOff>2971800</xdr:colOff>
-          <xdr:row>18</xdr:row>
-          <xdr:rowOff>1476375</xdr:rowOff>
+          <xdr:row>19</xdr:row>
+          <xdr:rowOff>3175</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2462,8 +2472,8 @@
         <xdr:to>
           <xdr:col>10</xdr:col>
           <xdr:colOff>2971800</xdr:colOff>
-          <xdr:row>19</xdr:row>
-          <xdr:rowOff>1476375</xdr:rowOff>
+          <xdr:row>20</xdr:row>
+          <xdr:rowOff>3175</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2518,7 +2528,7 @@
           <xdr:col>10</xdr:col>
           <xdr:colOff>2714625</xdr:colOff>
           <xdr:row>54</xdr:row>
-          <xdr:rowOff>1476375</xdr:rowOff>
+          <xdr:rowOff>1476374</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2572,8 +2582,8 @@
         <xdr:to>
           <xdr:col>10</xdr:col>
           <xdr:colOff>2714625</xdr:colOff>
-          <xdr:row>54</xdr:row>
-          <xdr:rowOff>1685925</xdr:rowOff>
+          <xdr:row>55</xdr:row>
+          <xdr:rowOff>2117</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2627,8 +2637,8 @@
         <xdr:to>
           <xdr:col>10</xdr:col>
           <xdr:colOff>2714625</xdr:colOff>
-          <xdr:row>55</xdr:row>
-          <xdr:rowOff>1685925</xdr:rowOff>
+          <xdr:row>56</xdr:row>
+          <xdr:rowOff>2117</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2682,8 +2692,8 @@
         <xdr:to>
           <xdr:col>10</xdr:col>
           <xdr:colOff>2714625</xdr:colOff>
-          <xdr:row>56</xdr:row>
-          <xdr:rowOff>1685925</xdr:rowOff>
+          <xdr:row>57</xdr:row>
+          <xdr:rowOff>2116</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2737,8 +2747,8 @@
         <xdr:to>
           <xdr:col>10</xdr:col>
           <xdr:colOff>2714625</xdr:colOff>
-          <xdr:row>57</xdr:row>
-          <xdr:rowOff>1685925</xdr:rowOff>
+          <xdr:row>58</xdr:row>
+          <xdr:rowOff>2117</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2792,8 +2802,8 @@
         <xdr:to>
           <xdr:col>10</xdr:col>
           <xdr:colOff>2714625</xdr:colOff>
-          <xdr:row>58</xdr:row>
-          <xdr:rowOff>1685925</xdr:rowOff>
+          <xdr:row>59</xdr:row>
+          <xdr:rowOff>2117</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2847,8 +2857,8 @@
         <xdr:to>
           <xdr:col>10</xdr:col>
           <xdr:colOff>2714625</xdr:colOff>
-          <xdr:row>59</xdr:row>
-          <xdr:rowOff>1685925</xdr:rowOff>
+          <xdr:row>60</xdr:row>
+          <xdr:rowOff>2116</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2902,8 +2912,8 @@
         <xdr:to>
           <xdr:col>10</xdr:col>
           <xdr:colOff>2714625</xdr:colOff>
-          <xdr:row>60</xdr:row>
-          <xdr:rowOff>1685925</xdr:rowOff>
+          <xdr:row>61</xdr:row>
+          <xdr:rowOff>2117</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2957,8 +2967,8 @@
         <xdr:to>
           <xdr:col>10</xdr:col>
           <xdr:colOff>2714625</xdr:colOff>
-          <xdr:row>61</xdr:row>
-          <xdr:rowOff>1685925</xdr:rowOff>
+          <xdr:row>62</xdr:row>
+          <xdr:rowOff>2117</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3300,7 +3310,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBADC660-92E1-2846-91C8-52CF36C59EA8}">
-  <dimension ref="E6:G14"/>
+  <dimension ref="E6:G12"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="17" customWidth="1"/>
@@ -3311,79 +3321,61 @@
     <row r="6" spans="5:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="7" spans="5:7" ht="18.75" x14ac:dyDescent="0.3">
       <c r="E7" s="40" t="s">
-        <v>257</v>
+        <v>203</v>
       </c>
       <c r="F7" s="36" t="s">
-        <v>258</v>
+        <v>204</v>
       </c>
       <c r="G7" s="66" t="s">
-        <v>256</v>
+        <v>202</v>
       </c>
     </row>
     <row r="8" spans="5:7" ht="18.75" x14ac:dyDescent="0.3">
       <c r="E8" s="41" t="s">
-        <v>259</v>
+        <v>205</v>
       </c>
       <c r="F8" s="37" t="s">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="G8" s="67"/>
     </row>
     <row r="9" spans="5:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E9" s="41" t="s">
-        <v>261</v>
+        <v>207</v>
       </c>
       <c r="F9" s="37" t="s">
-        <v>318</v>
+        <v>252</v>
       </c>
       <c r="G9" s="68"/>
     </row>
     <row r="10" spans="5:7" ht="18.75" x14ac:dyDescent="0.3">
       <c r="E10" s="41" t="s">
-        <v>262</v>
+        <v>208</v>
       </c>
       <c r="F10" s="32" t="s">
-        <v>263</v>
+        <v>209</v>
       </c>
       <c r="G10" s="35" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="11" spans="5:7" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="E11" s="41"/>
-      <c r="F11" s="32" t="s">
-        <v>265</v>
-      </c>
-      <c r="G11" s="33" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="12" spans="5:7" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="E12" s="41"/>
-      <c r="F12" s="32" t="s">
-        <v>266</v>
-      </c>
-      <c r="G12" s="33" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="13" spans="5:7" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="E13" s="42" t="s">
-        <v>268</v>
-      </c>
-      <c r="F13" s="38" t="s">
-        <v>271</v>
-      </c>
-      <c r="G13" s="33"/>
-    </row>
-    <row r="14" spans="5:7" ht="23.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E14" s="43" t="s">
-        <v>269</v>
-      </c>
-      <c r="F14" s="39" t="s">
-        <v>270</v>
-      </c>
-      <c r="G14" s="34"/>
+        <v>210</v>
+      </c>
+    </row>
+    <row r="11" spans="5:7" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="E11" s="42" t="s">
+        <v>211</v>
+      </c>
+      <c r="F11" s="38" t="s">
+        <v>214</v>
+      </c>
+      <c r="G11" s="33"/>
+    </row>
+    <row r="12" spans="5:7" ht="23.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E12" s="43" t="s">
+        <v>212</v>
+      </c>
+      <c r="F12" s="39" t="s">
+        <v>213</v>
+      </c>
+      <c r="G12" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3415,7 +3407,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -3538,7 +3530,7 @@
         <v>13</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D10" s="10">
         <v>1</v>
@@ -3566,7 +3558,7 @@
         <v>13</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="D12" s="10">
         <v>1</v>
@@ -3580,7 +3572,7 @@
         <v>16</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="D13" s="10">
         <v>1</v>
@@ -3594,7 +3586,7 @@
         <v>16</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="D14" s="10">
         <v>1</v>
@@ -3622,7 +3614,7 @@
         <v>16</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>149</v>
+        <v>319</v>
       </c>
       <c r="D16" s="10">
         <v>1</v>
@@ -3706,7 +3698,7 @@
         <v>25</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>181</v>
+        <v>158</v>
       </c>
       <c r="D22" s="10">
         <v>1</v>
@@ -3734,7 +3726,7 @@
         <v>26</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>189</v>
+        <v>163</v>
       </c>
       <c r="D24" s="10">
         <v>1</v>
@@ -3958,7 +3950,7 @@
         <v>28</v>
       </c>
       <c r="C40" s="15" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="D40" s="10">
         <v>9</v>
@@ -3986,7 +3978,7 @@
         <v>28</v>
       </c>
       <c r="C42" s="15" t="s">
-        <v>45</v>
+        <v>196</v>
       </c>
       <c r="D42" s="10">
         <v>1</v>
@@ -3997,10 +3989,10 @@
         <v>42</v>
       </c>
       <c r="B43" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="C43" s="15" t="s">
         <v>46</v>
-      </c>
-      <c r="C43" s="15" t="s">
-        <v>47</v>
       </c>
       <c r="D43" s="10">
         <v>1</v>
@@ -4011,10 +4003,10 @@
         <v>43</v>
       </c>
       <c r="B44" s="15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C44" s="15" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D44" s="10">
         <v>1</v>
@@ -4025,10 +4017,10 @@
         <v>44</v>
       </c>
       <c r="B45" s="15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C45" s="15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D45" s="10">
         <v>1</v>
@@ -4039,10 +4031,10 @@
         <v>45</v>
       </c>
       <c r="B46" s="15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C46" s="15" t="s">
-        <v>254</v>
+        <v>201</v>
       </c>
       <c r="D46" s="10">
         <v>1</v>
@@ -4063,7 +4055,7 @@
     <col min="2" max="2" width="23" customWidth="1"/>
     <col min="3" max="3" width="11.5" style="21" customWidth="1"/>
     <col min="4" max="4" width="48.875" style="5" customWidth="1"/>
-    <col min="5" max="5" width="54.5" style="5" customWidth="1"/>
+    <col min="5" max="5" width="62.875" style="5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="52.5" style="5" customWidth="1"/>
     <col min="7" max="7" width="25.875" style="6" customWidth="1"/>
     <col min="8" max="8" width="50.5" style="21" customWidth="1"/>
@@ -4072,47 +4064,47 @@
     <col min="11" max="11" width="40.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="7" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="C1" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="D1" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="E1" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="F1" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="G1" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="H1" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="H1" s="20" t="s">
+      <c r="I1" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="J1" s="65" t="s">
         <v>59</v>
       </c>
-      <c r="J1" s="65" t="s">
-        <v>60</v>
-      </c>
       <c r="K1" s="8" t="s">
-        <v>256</v>
+        <v>202</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="96.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="B2" s="16" t="s">
         <v>62</v>
-      </c>
-      <c r="B2" s="16" t="s">
-        <v>63</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>3</v>
@@ -4121,27 +4113,29 @@
         <v>4</v>
       </c>
       <c r="E2" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>73</v>
-      </c>
-      <c r="G2" s="18" t="s">
-        <v>64</v>
+        <v>71</v>
+      </c>
+      <c r="G2" s="69" t="s">
+        <v>253</v>
       </c>
       <c r="H2" s="17" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>254</v>
+      </c>
       <c r="K2" s="1"/>
     </row>
     <row r="3" spans="1:11" ht="93.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C3" s="14" t="s">
         <v>3</v>
@@ -4150,27 +4144,29 @@
         <v>4</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F3" s="17" t="s">
-        <v>74</v>
-      </c>
-      <c r="G3" s="18" t="s">
-        <v>77</v>
+        <v>72</v>
+      </c>
+      <c r="G3" s="69" t="s">
+        <v>255</v>
       </c>
       <c r="H3" s="14" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
+      <c r="J3" s="1" t="s">
+        <v>256</v>
+      </c>
       <c r="K3" s="1"/>
     </row>
     <row r="4" spans="1:11" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="16" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C4" s="14" t="s">
         <v>3</v>
@@ -4179,27 +4175,29 @@
         <v>4</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F4" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="G4" s="69" t="s">
+        <v>257</v>
+      </c>
+      <c r="H4" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="G4" s="18" t="s">
-        <v>79</v>
-      </c>
-      <c r="H4" s="14" t="s">
-        <v>78</v>
-      </c>
       <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
+      <c r="J4" s="1" t="s">
+        <v>256</v>
+      </c>
       <c r="K4" s="1"/>
     </row>
     <row r="5" spans="1:11" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C5" s="14" t="s">
         <v>3</v>
@@ -4208,74 +4206,76 @@
         <v>4</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F5" s="17" t="s">
-        <v>76</v>
-      </c>
-      <c r="G5" s="18" t="s">
-        <v>80</v>
+        <v>74</v>
+      </c>
+      <c r="G5" s="69" t="s">
+        <v>258</v>
       </c>
       <c r="H5" s="14" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
+      <c r="J5" s="1" t="s">
+        <v>256</v>
+      </c>
       <c r="K5" s="1"/>
     </row>
     <row r="6" spans="1:11" ht="62.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C6" s="14" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="F6" s="19" t="s">
+        <v>259</v>
+      </c>
+      <c r="G6" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="H6" s="14" t="s">
         <v>87</v>
-      </c>
-      <c r="E6" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="F6" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="G6" s="18" t="s">
-        <v>88</v>
-      </c>
-      <c r="H6" s="14" t="s">
-        <v>93</v>
       </c>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
     </row>
-    <row r="7" spans="1:11" ht="129.94999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" ht="110.25" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C7" s="14" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>97</v>
+        <v>260</v>
       </c>
       <c r="G7" s="18" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="H7" s="14" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
@@ -4283,10 +4283,10 @@
     </row>
     <row r="8" spans="1:11" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C8" s="14" t="s">
         <v>3</v>
@@ -4295,16 +4295,16 @@
         <v>7</v>
       </c>
       <c r="E8" s="16" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="F8" s="19" t="s">
-        <v>95</v>
+        <v>261</v>
       </c>
       <c r="G8" s="18" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="H8" s="23" t="s">
-        <v>96</v>
+        <v>262</v>
       </c>
       <c r="I8" s="24"/>
       <c r="J8" s="24"/>
@@ -4312,10 +4312,10 @@
     </row>
     <row r="9" spans="1:11" ht="110.25" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
-        <v>274</v>
+        <v>217</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C9" s="14" t="s">
         <v>8</v>
@@ -4324,16 +4324,16 @@
         <v>9</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>306</v>
+        <v>263</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>102</v>
+        <v>264</v>
       </c>
       <c r="G9" s="22" t="s">
-        <v>286</v>
+        <v>229</v>
       </c>
       <c r="H9" s="63" t="s">
-        <v>289</v>
+        <v>232</v>
       </c>
       <c r="I9" s="26"/>
       <c r="J9" s="26"/>
@@ -4341,28 +4341,28 @@
     </row>
     <row r="10" spans="1:11" ht="110.25" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
-        <v>275</v>
+        <v>218</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C10" s="14" t="s">
         <v>8</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>307</v>
+        <v>247</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>306</v>
+        <v>263</v>
       </c>
       <c r="F10" s="19" t="s">
-        <v>102</v>
+        <v>264</v>
       </c>
       <c r="G10" s="22" t="s">
-        <v>287</v>
+        <v>230</v>
       </c>
       <c r="H10" s="63" t="s">
-        <v>290</v>
+        <v>233</v>
       </c>
       <c r="I10" s="26"/>
       <c r="J10" s="26"/>
@@ -4370,28 +4370,28 @@
     </row>
     <row r="11" spans="1:11" ht="110.25" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
-        <v>276</v>
+        <v>219</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C11" s="14" t="s">
         <v>8</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>307</v>
+        <v>247</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>306</v>
+        <v>263</v>
       </c>
       <c r="F11" s="19" t="s">
-        <v>102</v>
+        <v>264</v>
       </c>
       <c r="G11" s="22" t="s">
-        <v>288</v>
+        <v>231</v>
       </c>
       <c r="H11" s="63" t="s">
-        <v>317</v>
+        <v>251</v>
       </c>
       <c r="I11" s="26"/>
       <c r="J11" s="26"/>
@@ -4399,28 +4399,28 @@
     </row>
     <row r="12" spans="1:11" ht="110.25" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
-        <v>277</v>
+        <v>220</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C12" s="14" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>307</v>
+        <v>247</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>308</v>
+        <v>265</v>
       </c>
       <c r="F12" s="19" t="s">
-        <v>102</v>
+        <v>264</v>
       </c>
       <c r="G12" s="22" t="s">
-        <v>286</v>
+        <v>229</v>
       </c>
       <c r="H12" s="63" t="s">
-        <v>291</v>
+        <v>234</v>
       </c>
       <c r="I12" s="26"/>
       <c r="J12" s="26"/>
@@ -4428,57 +4428,57 @@
     </row>
     <row r="13" spans="1:11" ht="110.25" x14ac:dyDescent="0.25">
       <c r="A13" s="16" t="s">
-        <v>278</v>
+        <v>221</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C13" s="14" t="s">
         <v>8</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>307</v>
+        <v>247</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>308</v>
+        <v>265</v>
       </c>
       <c r="F13" s="19" t="s">
-        <v>102</v>
+        <v>264</v>
       </c>
       <c r="G13" s="22" t="s">
-        <v>287</v>
+        <v>230</v>
       </c>
       <c r="H13" s="63" t="s">
-        <v>292</v>
+        <v>235</v>
       </c>
       <c r="I13" s="26"/>
       <c r="J13" s="26"/>
       <c r="K13" s="26"/>
     </row>
-    <row r="14" spans="1:11" ht="128.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" ht="110.25" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
-        <v>279</v>
+        <v>222</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C14" s="14" t="s">
         <v>8</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>307</v>
+        <v>247</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>308</v>
+        <v>265</v>
       </c>
       <c r="F14" s="19" t="s">
-        <v>102</v>
+        <v>264</v>
       </c>
       <c r="G14" s="22" t="s">
-        <v>288</v>
+        <v>231</v>
       </c>
       <c r="H14" s="63" t="s">
-        <v>317</v>
+        <v>251</v>
       </c>
       <c r="I14" s="26"/>
       <c r="J14" s="26"/>
@@ -4486,28 +4486,28 @@
     </row>
     <row r="15" spans="1:11" ht="110.25" x14ac:dyDescent="0.25">
       <c r="A15" s="16" t="s">
-        <v>280</v>
+        <v>223</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C15" s="14" t="s">
         <v>8</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>307</v>
+        <v>247</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>309</v>
+        <v>266</v>
       </c>
       <c r="F15" s="19" t="s">
-        <v>102</v>
+        <v>264</v>
       </c>
       <c r="G15" s="22" t="s">
-        <v>286</v>
+        <v>229</v>
       </c>
       <c r="H15" s="63" t="s">
-        <v>293</v>
+        <v>236</v>
       </c>
       <c r="I15" s="26"/>
       <c r="J15" s="26"/>
@@ -4515,28 +4515,28 @@
     </row>
     <row r="16" spans="1:11" ht="110.25" x14ac:dyDescent="0.25">
       <c r="A16" s="16" t="s">
-        <v>281</v>
+        <v>224</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C16" s="14" t="s">
         <v>8</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>307</v>
+        <v>247</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>309</v>
+        <v>266</v>
       </c>
       <c r="F16" s="19" t="s">
-        <v>102</v>
+        <v>264</v>
       </c>
       <c r="G16" s="22" t="s">
-        <v>287</v>
+        <v>230</v>
       </c>
       <c r="H16" s="63" t="s">
-        <v>294</v>
+        <v>237</v>
       </c>
       <c r="I16" s="26"/>
       <c r="J16" s="26"/>
@@ -4544,28 +4544,28 @@
     </row>
     <row r="17" spans="1:11" ht="110.25" x14ac:dyDescent="0.25">
       <c r="A17" s="16" t="s">
-        <v>282</v>
+        <v>225</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C17" s="14" t="s">
         <v>8</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>307</v>
+        <v>247</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>309</v>
+        <v>266</v>
       </c>
       <c r="F17" s="19" t="s">
-        <v>102</v>
+        <v>264</v>
       </c>
       <c r="G17" s="22" t="s">
-        <v>288</v>
+        <v>231</v>
       </c>
       <c r="H17" s="63" t="s">
-        <v>317</v>
+        <v>251</v>
       </c>
       <c r="I17" s="26"/>
       <c r="J17" s="26"/>
@@ -4573,10 +4573,10 @@
     </row>
     <row r="18" spans="1:11" ht="110.25" x14ac:dyDescent="0.25">
       <c r="A18" s="16" t="s">
-        <v>283</v>
+        <v>226</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C18" s="14" t="s">
         <v>8</v>
@@ -4585,16 +4585,16 @@
         <v>9</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>310</v>
+        <v>267</v>
       </c>
       <c r="F18" s="19" t="s">
-        <v>102</v>
+        <v>264</v>
       </c>
       <c r="G18" s="22" t="s">
-        <v>286</v>
+        <v>229</v>
       </c>
       <c r="H18" s="63" t="s">
-        <v>317</v>
+        <v>251</v>
       </c>
       <c r="I18" s="26"/>
       <c r="J18" s="26"/>
@@ -4602,28 +4602,28 @@
     </row>
     <row r="19" spans="1:11" ht="110.25" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="s">
-        <v>284</v>
+        <v>227</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C19" s="14" t="s">
         <v>8</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>307</v>
+        <v>247</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>310</v>
+        <v>267</v>
       </c>
       <c r="F19" s="19" t="s">
-        <v>102</v>
+        <v>264</v>
       </c>
       <c r="G19" s="22" t="s">
-        <v>287</v>
+        <v>230</v>
       </c>
       <c r="H19" s="63" t="s">
-        <v>317</v>
+        <v>251</v>
       </c>
       <c r="I19" s="26"/>
       <c r="J19" s="26"/>
@@ -4631,28 +4631,28 @@
     </row>
     <row r="20" spans="1:11" ht="110.25" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
-        <v>285</v>
+        <v>228</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C20" s="14" t="s">
         <v>8</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>307</v>
+        <v>247</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>310</v>
+        <v>267</v>
       </c>
       <c r="F20" s="19" t="s">
-        <v>102</v>
+        <v>264</v>
       </c>
       <c r="G20" s="22" t="s">
-        <v>288</v>
+        <v>231</v>
       </c>
       <c r="H20" s="63" t="s">
-        <v>317</v>
+        <v>251</v>
       </c>
       <c r="I20" s="26"/>
       <c r="J20" s="26"/>
@@ -4660,10 +4660,10 @@
     </row>
     <row r="21" spans="1:11" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C21" s="14" t="s">
         <v>10</v>
@@ -4672,16 +4672,16 @@
         <v>11</v>
       </c>
       <c r="E21" s="16" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="F21" s="19" t="s">
-        <v>105</v>
+        <v>268</v>
       </c>
       <c r="G21" s="22" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="H21" s="30" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="I21" s="28"/>
       <c r="J21" s="29"/>
@@ -4689,10 +4689,10 @@
     </row>
     <row r="22" spans="1:11" ht="157.5" x14ac:dyDescent="0.25">
       <c r="A22" s="16" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C22" s="14" t="s">
         <v>10</v>
@@ -4701,16 +4701,16 @@
         <v>12</v>
       </c>
       <c r="E22" s="16" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="F22" s="19" t="s">
-        <v>107</v>
+        <v>269</v>
       </c>
       <c r="G22" s="22" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="H22" s="14" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="I22" s="25"/>
       <c r="J22" s="27"/>
@@ -4718,10 +4718,10 @@
     </row>
     <row r="23" spans="1:11" ht="141.75" x14ac:dyDescent="0.25">
       <c r="A23" s="16" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C23" s="14" t="s">
         <v>13</v>
@@ -4730,16 +4730,16 @@
         <v>14</v>
       </c>
       <c r="E23" s="16" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="F23" s="19" t="s">
-        <v>143</v>
+        <v>270</v>
       </c>
       <c r="G23" s="22" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="H23" s="31" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="I23" s="25"/>
       <c r="J23" s="27"/>
@@ -4747,28 +4747,28 @@
     </row>
     <row r="24" spans="1:11" ht="141.75" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C24" s="14" t="s">
         <v>13</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E24" s="16" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="F24" s="19" t="s">
-        <v>143</v>
+        <v>270</v>
       </c>
       <c r="G24" s="18" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="H24" s="31" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="I24" s="25"/>
       <c r="J24" s="25"/>
@@ -4776,10 +4776,10 @@
     </row>
     <row r="25" spans="1:11" ht="126" x14ac:dyDescent="0.25">
       <c r="A25" s="16" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C25" s="14" t="s">
         <v>13</v>
@@ -4788,16 +4788,16 @@
         <v>15</v>
       </c>
       <c r="E25" s="16" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="F25" s="19" t="s">
-        <v>145</v>
+        <v>271</v>
       </c>
       <c r="G25" s="18" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="H25" s="31" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="I25" s="25"/>
       <c r="J25" s="25"/>
@@ -4805,28 +4805,28 @@
     </row>
     <row r="26" spans="1:11" ht="126" x14ac:dyDescent="0.25">
       <c r="A26" s="16" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C26" s="14" t="s">
         <v>13</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="E26" s="16" t="s">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="F26" s="19" t="s">
-        <v>253</v>
+        <v>272</v>
       </c>
       <c r="G26" s="18" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="H26" s="31" t="s">
-        <v>153</v>
+        <v>138</v>
       </c>
       <c r="I26" s="25"/>
       <c r="J26" s="25"/>
@@ -4834,28 +4834,28 @@
     </row>
     <row r="27" spans="1:11" ht="126" x14ac:dyDescent="0.25">
       <c r="A27" s="16" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C27" s="14" t="s">
         <v>16</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="E27" s="16" t="s">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="F27" s="19" t="s">
-        <v>157</v>
+        <v>273</v>
       </c>
       <c r="G27" s="18" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="H27" s="31" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
@@ -4863,28 +4863,28 @@
     </row>
     <row r="28" spans="1:11" ht="126" x14ac:dyDescent="0.25">
       <c r="A28" s="16" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C28" s="14" t="s">
         <v>16</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>156</v>
+        <v>141</v>
       </c>
       <c r="F28" s="19" t="s">
-        <v>157</v>
+        <v>273</v>
       </c>
       <c r="G28" s="18" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="H28" s="31" t="s">
-        <v>160</v>
+        <v>143</v>
       </c>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
@@ -4892,10 +4892,10 @@
     </row>
     <row r="29" spans="1:11" ht="126" x14ac:dyDescent="0.25">
       <c r="A29" s="16" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C29" s="14" t="s">
         <v>16</v>
@@ -4904,16 +4904,16 @@
         <v>17</v>
       </c>
       <c r="E29" s="16" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="F29" s="19" t="s">
-        <v>158</v>
+        <v>274</v>
       </c>
       <c r="G29" s="18" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="H29" s="31" t="s">
-        <v>161</v>
+        <v>144</v>
       </c>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
@@ -4921,28 +4921,28 @@
     </row>
     <row r="30" spans="1:11" ht="126" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C30" s="14" t="s">
         <v>16</v>
       </c>
       <c r="D30" s="14" t="s">
-        <v>174</v>
+        <v>154</v>
       </c>
       <c r="E30" s="16" t="s">
-        <v>175</v>
+        <v>155</v>
       </c>
       <c r="F30" s="19" t="s">
-        <v>252</v>
+        <v>275</v>
       </c>
       <c r="G30" s="18" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="H30" s="31" t="s">
-        <v>165</v>
+        <v>148</v>
       </c>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
@@ -4950,10 +4950,10 @@
     </row>
     <row r="31" spans="1:11" ht="126" x14ac:dyDescent="0.25">
       <c r="A31" s="16" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C31" s="14" t="s">
         <v>18</v>
@@ -4962,16 +4962,16 @@
         <v>19</v>
       </c>
       <c r="E31" s="16" t="s">
-        <v>163</v>
+        <v>146</v>
       </c>
       <c r="F31" s="19" t="s">
-        <v>169</v>
+        <v>276</v>
       </c>
       <c r="G31" s="18" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="H31" s="31" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
@@ -4979,28 +4979,28 @@
     </row>
     <row r="32" spans="1:11" ht="157.5" x14ac:dyDescent="0.25">
       <c r="A32" s="16" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C32" s="14" t="s">
         <v>18</v>
       </c>
       <c r="D32" s="14" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="E32" s="16" t="s">
-        <v>164</v>
+        <v>147</v>
       </c>
       <c r="F32" s="19" t="s">
-        <v>171</v>
+        <v>277</v>
       </c>
       <c r="G32" s="18" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="H32" s="31" t="s">
-        <v>167</v>
+        <v>150</v>
       </c>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
@@ -5008,10 +5008,10 @@
     </row>
     <row r="33" spans="1:11" ht="126" x14ac:dyDescent="0.25">
       <c r="A33" s="16" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="B33" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C33" s="14" t="s">
         <v>18</v>
@@ -5020,16 +5020,16 @@
         <v>21</v>
       </c>
       <c r="E33" s="16" t="s">
-        <v>168</v>
+        <v>151</v>
       </c>
       <c r="F33" s="19" t="s">
-        <v>172</v>
+        <v>278</v>
       </c>
       <c r="G33" s="18" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="H33" s="31" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
@@ -5037,28 +5037,28 @@
     </row>
     <row r="34" spans="1:11" ht="126" x14ac:dyDescent="0.25">
       <c r="A34" s="16" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="B34" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C34" s="14" t="s">
         <v>18</v>
       </c>
       <c r="D34" s="14" t="s">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="E34" s="16" t="s">
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="F34" s="19" t="s">
-        <v>251</v>
+        <v>279</v>
       </c>
       <c r="G34" s="18" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="H34" s="31" t="s">
-        <v>165</v>
+        <v>148</v>
       </c>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
@@ -5066,10 +5066,10 @@
     </row>
     <row r="35" spans="1:11" ht="141.75" x14ac:dyDescent="0.25">
       <c r="A35" s="16" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="B35" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C35" s="14" t="s">
         <v>23</v>
@@ -5078,16 +5078,16 @@
         <v>24</v>
       </c>
       <c r="E35" s="16" t="s">
-        <v>180</v>
+        <v>157</v>
       </c>
       <c r="F35" s="19" t="s">
-        <v>177</v>
+        <v>280</v>
       </c>
       <c r="G35" s="18" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="H35" s="23" t="s">
-        <v>178</v>
+        <v>281</v>
       </c>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
@@ -5095,28 +5095,28 @@
     </row>
     <row r="36" spans="1:11" ht="126" x14ac:dyDescent="0.25">
       <c r="A36" s="16" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="B36" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C36" s="14" t="s">
         <v>25</v>
       </c>
       <c r="D36" s="14" t="s">
-        <v>181</v>
+        <v>158</v>
       </c>
       <c r="E36" s="16" t="s">
-        <v>179</v>
+        <v>282</v>
       </c>
       <c r="F36" s="19" t="s">
-        <v>182</v>
+        <v>283</v>
       </c>
       <c r="G36" s="18" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="H36" s="23" t="s">
-        <v>183</v>
+        <v>284</v>
       </c>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
@@ -5124,28 +5124,28 @@
     </row>
     <row r="37" spans="1:11" ht="63" x14ac:dyDescent="0.25">
       <c r="A37" s="16" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="B37" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C37" s="14" t="s">
         <v>26</v>
       </c>
       <c r="D37" s="14" t="s">
-        <v>184</v>
+        <v>159</v>
       </c>
       <c r="E37" s="16" t="s">
-        <v>186</v>
+        <v>160</v>
       </c>
       <c r="F37" s="19" t="s">
-        <v>185</v>
+        <v>285</v>
       </c>
       <c r="G37" s="18" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="H37" s="14" t="s">
-        <v>187</v>
+        <v>161</v>
       </c>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
@@ -5153,28 +5153,28 @@
     </row>
     <row r="38" spans="1:11" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A38" s="16" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="B38" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C38" s="14" t="s">
         <v>26</v>
       </c>
       <c r="D38" s="14" t="s">
-        <v>189</v>
+        <v>163</v>
       </c>
       <c r="E38" s="16" t="s">
-        <v>190</v>
+        <v>164</v>
       </c>
       <c r="F38" s="19" t="s">
-        <v>191</v>
+        <v>286</v>
       </c>
       <c r="G38" s="18" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="H38" s="17" t="s">
-        <v>192</v>
+        <v>287</v>
       </c>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
@@ -5182,10 +5182,10 @@
     </row>
     <row r="39" spans="1:11" ht="126" x14ac:dyDescent="0.25">
       <c r="A39" s="16" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="B39" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C39" s="14" t="s">
         <v>28</v>
@@ -5194,16 +5194,16 @@
         <v>29</v>
       </c>
       <c r="E39" s="16" t="s">
-        <v>195</v>
+        <v>167</v>
       </c>
       <c r="F39" s="19" t="s">
-        <v>198</v>
+        <v>288</v>
       </c>
       <c r="G39" s="18" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="H39" s="31" t="s">
-        <v>193</v>
+        <v>165</v>
       </c>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
@@ -5211,10 +5211,10 @@
     </row>
     <row r="40" spans="1:11" ht="126" x14ac:dyDescent="0.25">
       <c r="A40" s="16" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="B40" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C40" s="14" t="s">
         <v>28</v>
@@ -5223,16 +5223,16 @@
         <v>30</v>
       </c>
       <c r="E40" s="16" t="s">
-        <v>194</v>
+        <v>166</v>
       </c>
       <c r="F40" s="19" t="s">
-        <v>198</v>
+        <v>288</v>
       </c>
       <c r="G40" s="18" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="H40" s="31" t="s">
-        <v>196</v>
+        <v>168</v>
       </c>
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
@@ -5240,10 +5240,10 @@
     </row>
     <row r="41" spans="1:11" ht="141.75" x14ac:dyDescent="0.25">
       <c r="A41" s="16" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="B41" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C41" s="14" t="s">
         <v>28</v>
@@ -5252,16 +5252,16 @@
         <v>31</v>
       </c>
       <c r="E41" s="16" t="s">
-        <v>197</v>
+        <v>169</v>
       </c>
       <c r="F41" s="19" t="s">
-        <v>199</v>
+        <v>289</v>
       </c>
       <c r="G41" s="18" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="H41" s="31" t="s">
-        <v>200</v>
+        <v>170</v>
       </c>
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
@@ -5269,10 +5269,10 @@
     </row>
     <row r="42" spans="1:11" ht="126" x14ac:dyDescent="0.25">
       <c r="A42" s="16" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="B42" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C42" s="14" t="s">
         <v>28</v>
@@ -5281,16 +5281,16 @@
         <v>33</v>
       </c>
       <c r="E42" s="16" t="s">
-        <v>201</v>
+        <v>171</v>
       </c>
       <c r="F42" s="19" t="s">
-        <v>204</v>
+        <v>290</v>
       </c>
       <c r="G42" s="18" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="H42" s="31" t="s">
-        <v>205</v>
+        <v>174</v>
       </c>
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
@@ -5298,10 +5298,10 @@
     </row>
     <row r="43" spans="1:11" ht="126" x14ac:dyDescent="0.25">
       <c r="A43" s="16" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="B43" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C43" s="14" t="s">
         <v>28</v>
@@ -5310,16 +5310,16 @@
         <v>32</v>
       </c>
       <c r="E43" s="16" t="s">
-        <v>202</v>
+        <v>172</v>
       </c>
       <c r="F43" s="19" t="s">
-        <v>204</v>
+        <v>290</v>
       </c>
       <c r="G43" s="18" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="H43" s="31" t="s">
-        <v>206</v>
+        <v>175</v>
       </c>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
@@ -5327,10 +5327,10 @@
     </row>
     <row r="44" spans="1:11" ht="126" x14ac:dyDescent="0.25">
       <c r="A44" s="16" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="B44" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C44" s="14" t="s">
         <v>28</v>
@@ -5339,16 +5339,16 @@
         <v>34</v>
       </c>
       <c r="E44" s="16" t="s">
-        <v>203</v>
+        <v>173</v>
       </c>
       <c r="F44" s="19" t="s">
-        <v>208</v>
+        <v>291</v>
       </c>
       <c r="G44" s="18" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="H44" s="31" t="s">
-        <v>207</v>
+        <v>176</v>
       </c>
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
@@ -5356,10 +5356,10 @@
     </row>
     <row r="45" spans="1:11" ht="110.25" x14ac:dyDescent="0.25">
       <c r="A45" s="16" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="B45" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C45" s="14" t="s">
         <v>28</v>
@@ -5368,16 +5368,16 @@
         <v>35</v>
       </c>
       <c r="E45" s="16" t="s">
-        <v>209</v>
+        <v>177</v>
       </c>
       <c r="F45" s="19" t="s">
-        <v>210</v>
+        <v>292</v>
       </c>
       <c r="G45" s="18" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="H45" s="31" t="s">
-        <v>211</v>
+        <v>178</v>
       </c>
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
@@ -5385,10 +5385,10 @@
     </row>
     <row r="46" spans="1:11" ht="110.25" x14ac:dyDescent="0.25">
       <c r="A46" s="16" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="B46" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C46" s="14" t="s">
         <v>28</v>
@@ -5397,16 +5397,16 @@
         <v>36</v>
       </c>
       <c r="E46" s="16" t="s">
-        <v>212</v>
+        <v>179</v>
       </c>
       <c r="F46" s="19" t="s">
-        <v>210</v>
+        <v>292</v>
       </c>
       <c r="G46" s="18" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="H46" s="31" t="s">
-        <v>213</v>
+        <v>180</v>
       </c>
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
@@ -5414,10 +5414,10 @@
     </row>
     <row r="47" spans="1:11" ht="126" x14ac:dyDescent="0.25">
       <c r="A47" s="16" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="B47" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C47" s="14" t="s">
         <v>28</v>
@@ -5426,16 +5426,16 @@
         <v>37</v>
       </c>
       <c r="E47" s="16" t="s">
-        <v>214</v>
+        <v>181</v>
       </c>
       <c r="F47" s="19" t="s">
-        <v>215</v>
+        <v>293</v>
       </c>
       <c r="G47" s="18" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="H47" s="31" t="s">
-        <v>216</v>
+        <v>182</v>
       </c>
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
@@ -5443,10 +5443,10 @@
     </row>
     <row r="48" spans="1:11" ht="126" x14ac:dyDescent="0.25">
       <c r="A48" s="16" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="B48" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C48" s="14" t="s">
         <v>28</v>
@@ -5455,16 +5455,16 @@
         <v>38</v>
       </c>
       <c r="E48" s="16" t="s">
-        <v>217</v>
+        <v>183</v>
       </c>
       <c r="F48" s="19" t="s">
-        <v>218</v>
+        <v>294</v>
       </c>
       <c r="G48" s="18" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="H48" s="31" t="s">
-        <v>219</v>
+        <v>184</v>
       </c>
       <c r="I48" s="1"/>
       <c r="J48" s="1"/>
@@ -5472,10 +5472,10 @@
     </row>
     <row r="49" spans="1:11" ht="126" x14ac:dyDescent="0.25">
       <c r="A49" s="16" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="B49" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C49" s="14" t="s">
         <v>28</v>
@@ -5484,16 +5484,16 @@
         <v>39</v>
       </c>
       <c r="E49" s="16" t="s">
-        <v>220</v>
+        <v>185</v>
       </c>
       <c r="F49" s="19" t="s">
-        <v>218</v>
+        <v>294</v>
       </c>
       <c r="G49" s="18" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="H49" s="31" t="s">
-        <v>221</v>
+        <v>186</v>
       </c>
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
@@ -5501,10 +5501,10 @@
     </row>
     <row r="50" spans="1:11" ht="126" x14ac:dyDescent="0.25">
       <c r="A50" s="16" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="B50" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C50" s="14" t="s">
         <v>28</v>
@@ -5513,16 +5513,16 @@
         <v>40</v>
       </c>
       <c r="E50" s="16" t="s">
-        <v>222</v>
+        <v>187</v>
       </c>
       <c r="F50" s="19" t="s">
-        <v>223</v>
+        <v>295</v>
       </c>
       <c r="G50" s="18" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="H50" s="31" t="s">
-        <v>224</v>
+        <v>188</v>
       </c>
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
@@ -5530,10 +5530,10 @@
     </row>
     <row r="51" spans="1:11" ht="126" x14ac:dyDescent="0.25">
       <c r="A51" s="16" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="B51" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C51" s="14" t="s">
         <v>28</v>
@@ -5542,16 +5542,16 @@
         <v>41</v>
       </c>
       <c r="E51" s="16" t="s">
-        <v>226</v>
+        <v>190</v>
       </c>
       <c r="F51" s="19" t="s">
-        <v>227</v>
+        <v>296</v>
       </c>
       <c r="G51" s="18" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="H51" s="31" t="s">
-        <v>228</v>
+        <v>191</v>
       </c>
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
@@ -5559,10 +5559,10 @@
     </row>
     <row r="52" spans="1:11" ht="126" x14ac:dyDescent="0.25">
       <c r="A52" s="16" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="B52" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C52" s="14" t="s">
         <v>28</v>
@@ -5571,16 +5571,16 @@
         <v>42</v>
       </c>
       <c r="E52" s="16" t="s">
-        <v>229</v>
+        <v>192</v>
       </c>
       <c r="F52" s="19" t="s">
-        <v>227</v>
+        <v>296</v>
       </c>
       <c r="G52" s="18" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="H52" s="31" t="s">
-        <v>230</v>
+        <v>193</v>
       </c>
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
@@ -5588,10 +5588,10 @@
     </row>
     <row r="53" spans="1:11" ht="126" x14ac:dyDescent="0.25">
       <c r="A53" s="16" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="B53" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C53" s="14" t="s">
         <v>28</v>
@@ -5600,16 +5600,16 @@
         <v>43</v>
       </c>
       <c r="E53" s="16" t="s">
-        <v>231</v>
+        <v>194</v>
       </c>
       <c r="F53" s="19" t="s">
-        <v>232</v>
+        <v>297</v>
       </c>
       <c r="G53" s="18" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="H53" s="31" t="s">
-        <v>233</v>
+        <v>195</v>
       </c>
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
@@ -5617,28 +5617,28 @@
     </row>
     <row r="54" spans="1:11" ht="126" x14ac:dyDescent="0.25">
       <c r="A54" s="16" t="s">
-        <v>295</v>
+        <v>238</v>
       </c>
       <c r="B54" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C54" s="18" t="s">
         <v>28</v>
       </c>
       <c r="D54" s="14" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="E54" s="16" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="F54" s="19" t="s">
-        <v>244</v>
+        <v>300</v>
       </c>
       <c r="G54" s="18" t="s">
-        <v>311</v>
+        <v>248</v>
       </c>
       <c r="H54" s="31" t="s">
-        <v>314</v>
+        <v>301</v>
       </c>
       <c r="I54" s="1"/>
       <c r="J54" s="1"/>
@@ -5646,28 +5646,28 @@
     </row>
     <row r="55" spans="1:11" ht="126" x14ac:dyDescent="0.25">
       <c r="A55" s="16" t="s">
-        <v>296</v>
+        <v>239</v>
       </c>
       <c r="B55" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C55" s="18" t="s">
         <v>28</v>
       </c>
       <c r="D55" s="14" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="E55" s="16" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="F55" s="19" t="s">
-        <v>244</v>
+        <v>300</v>
       </c>
       <c r="G55" s="18" t="s">
-        <v>312</v>
+        <v>249</v>
       </c>
       <c r="H55" s="31" t="s">
-        <v>314</v>
+        <v>301</v>
       </c>
       <c r="I55" s="1"/>
       <c r="J55" s="1"/>
@@ -5675,28 +5675,28 @@
     </row>
     <row r="56" spans="1:11" ht="126" x14ac:dyDescent="0.25">
       <c r="A56" s="16" t="s">
-        <v>297</v>
+        <v>240</v>
       </c>
       <c r="B56" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C56" s="18" t="s">
         <v>28</v>
       </c>
       <c r="D56" s="14" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="E56" s="16" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="F56" s="19" t="s">
-        <v>244</v>
+        <v>300</v>
       </c>
       <c r="G56" s="18" t="s">
-        <v>313</v>
+        <v>250</v>
       </c>
       <c r="H56" s="63" t="s">
-        <v>317</v>
+        <v>251</v>
       </c>
       <c r="I56" s="1"/>
       <c r="J56" s="1"/>
@@ -5704,28 +5704,28 @@
     </row>
     <row r="57" spans="1:11" ht="126" x14ac:dyDescent="0.25">
       <c r="A57" s="16" t="s">
-        <v>298</v>
+        <v>241</v>
       </c>
       <c r="B57" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C57" s="18" t="s">
         <v>28</v>
       </c>
       <c r="D57" s="14" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="E57" s="16" t="s">
-        <v>240</v>
+        <v>302</v>
       </c>
       <c r="F57" s="19" t="s">
-        <v>244</v>
+        <v>300</v>
       </c>
       <c r="G57" s="18" t="s">
-        <v>311</v>
+        <v>248</v>
       </c>
       <c r="H57" s="31" t="s">
-        <v>314</v>
+        <v>301</v>
       </c>
       <c r="I57" s="1"/>
       <c r="J57" s="1"/>
@@ -5733,28 +5733,28 @@
     </row>
     <row r="58" spans="1:11" ht="126" x14ac:dyDescent="0.25">
       <c r="A58" s="16" t="s">
-        <v>299</v>
+        <v>242</v>
       </c>
       <c r="B58" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C58" s="18" t="s">
         <v>28</v>
       </c>
       <c r="D58" s="14" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="E58" s="16" t="s">
-        <v>240</v>
+        <v>302</v>
       </c>
       <c r="F58" s="19" t="s">
-        <v>244</v>
+        <v>300</v>
       </c>
       <c r="G58" s="18" t="s">
-        <v>312</v>
+        <v>249</v>
       </c>
       <c r="H58" s="31" t="s">
-        <v>314</v>
+        <v>301</v>
       </c>
       <c r="I58" s="1"/>
       <c r="J58" s="1"/>
@@ -5762,28 +5762,28 @@
     </row>
     <row r="59" spans="1:11" ht="126" x14ac:dyDescent="0.25">
       <c r="A59" s="16" t="s">
-        <v>300</v>
+        <v>243</v>
       </c>
       <c r="B59" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C59" s="18" t="s">
         <v>28</v>
       </c>
       <c r="D59" s="14" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="E59" s="16" t="s">
-        <v>240</v>
+        <v>302</v>
       </c>
       <c r="F59" s="19" t="s">
-        <v>244</v>
+        <v>300</v>
       </c>
       <c r="G59" s="18" t="s">
-        <v>313</v>
+        <v>250</v>
       </c>
       <c r="H59" s="63" t="s">
-        <v>317</v>
+        <v>251</v>
       </c>
       <c r="I59" s="1"/>
       <c r="J59" s="1"/>
@@ -5791,28 +5791,28 @@
     </row>
     <row r="60" spans="1:11" ht="126" x14ac:dyDescent="0.25">
       <c r="A60" s="16" t="s">
-        <v>301</v>
+        <v>244</v>
       </c>
       <c r="B60" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C60" s="18" t="s">
         <v>28</v>
       </c>
       <c r="D60" s="14" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="E60" s="16" t="s">
-        <v>240</v>
+        <v>302</v>
       </c>
       <c r="F60" s="19" t="s">
-        <v>244</v>
+        <v>300</v>
       </c>
       <c r="G60" s="18" t="s">
-        <v>311</v>
+        <v>248</v>
       </c>
       <c r="H60" s="31" t="s">
-        <v>314</v>
+        <v>301</v>
       </c>
       <c r="I60" s="1"/>
       <c r="J60" s="1"/>
@@ -5820,28 +5820,28 @@
     </row>
     <row r="61" spans="1:11" ht="126" x14ac:dyDescent="0.25">
       <c r="A61" s="16" t="s">
-        <v>302</v>
+        <v>245</v>
       </c>
       <c r="B61" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C61" s="18" t="s">
         <v>28</v>
       </c>
       <c r="D61" s="14" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="E61" s="16" t="s">
-        <v>240</v>
+        <v>302</v>
       </c>
       <c r="F61" s="19" t="s">
-        <v>244</v>
+        <v>300</v>
       </c>
       <c r="G61" s="18" t="s">
-        <v>312</v>
+        <v>249</v>
       </c>
       <c r="H61" s="31" t="s">
-        <v>314</v>
+        <v>301</v>
       </c>
       <c r="I61" s="1"/>
       <c r="J61" s="1"/>
@@ -5849,28 +5849,28 @@
     </row>
     <row r="62" spans="1:11" ht="126" x14ac:dyDescent="0.25">
       <c r="A62" s="16" t="s">
-        <v>303</v>
+        <v>246</v>
       </c>
       <c r="B62" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C62" s="18" t="s">
         <v>28</v>
       </c>
       <c r="D62" s="14" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="E62" s="16" t="s">
-        <v>240</v>
+        <v>302</v>
       </c>
       <c r="F62" s="19" t="s">
-        <v>244</v>
+        <v>300</v>
       </c>
       <c r="G62" s="18" t="s">
-        <v>313</v>
+        <v>250</v>
       </c>
       <c r="H62" s="63" t="s">
-        <v>317</v>
+        <v>251</v>
       </c>
       <c r="I62" s="1"/>
       <c r="J62" s="1"/>
@@ -5878,28 +5878,28 @@
     </row>
     <row r="63" spans="1:11" ht="126" x14ac:dyDescent="0.25">
       <c r="A63" s="16" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="B63" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C63" s="14" t="s">
         <v>28</v>
       </c>
       <c r="D63" s="14" t="s">
-        <v>44</v>
+        <v>303</v>
       </c>
       <c r="E63" s="16" t="s">
-        <v>234</v>
+        <v>304</v>
       </c>
       <c r="F63" s="19" t="s">
-        <v>316</v>
+        <v>305</v>
       </c>
       <c r="G63" s="18" t="s">
-        <v>241</v>
+        <v>198</v>
       </c>
       <c r="H63" s="31" t="s">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="I63" s="1"/>
       <c r="J63" s="1"/>
@@ -5907,28 +5907,28 @@
     </row>
     <row r="64" spans="1:11" ht="141.75" x14ac:dyDescent="0.25">
       <c r="A64" s="16" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="B64" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C64" s="14" t="s">
         <v>28</v>
       </c>
       <c r="D64" s="14" t="s">
-        <v>236</v>
+        <v>307</v>
       </c>
       <c r="E64" s="16" t="s">
-        <v>235</v>
+        <v>308</v>
       </c>
       <c r="F64" s="19" t="s">
-        <v>242</v>
+        <v>309</v>
       </c>
       <c r="G64" s="18" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="H64" s="31" t="s">
-        <v>243</v>
+        <v>310</v>
       </c>
       <c r="I64" s="1"/>
       <c r="J64" s="1"/>
@@ -5936,28 +5936,28 @@
     </row>
     <row r="65" spans="1:11" ht="157.5" x14ac:dyDescent="0.25">
       <c r="A65" s="16" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="B65" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C65" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="D65" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="D65" s="14" t="s">
-        <v>47</v>
-      </c>
       <c r="E65" s="16" t="s">
-        <v>237</v>
+        <v>311</v>
       </c>
       <c r="F65" s="19" t="s">
-        <v>245</v>
+        <v>312</v>
       </c>
       <c r="G65" s="18" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="H65" s="31" t="s">
-        <v>246</v>
+        <v>199</v>
       </c>
       <c r="I65" s="1"/>
       <c r="J65" s="1"/>
@@ -5965,28 +5965,28 @@
     </row>
     <row r="66" spans="1:11" ht="157.5" x14ac:dyDescent="0.25">
       <c r="A66" s="16" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="B66" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C66" s="14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D66" s="14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E66" s="16" t="s">
-        <v>238</v>
+        <v>313</v>
       </c>
       <c r="F66" s="19" t="s">
-        <v>245</v>
+        <v>312</v>
       </c>
       <c r="G66" s="18" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="H66" s="31" t="s">
-        <v>247</v>
+        <v>314</v>
       </c>
       <c r="I66" s="1"/>
       <c r="J66" s="1"/>
@@ -5994,28 +5994,28 @@
     </row>
     <row r="67" spans="1:11" ht="126" x14ac:dyDescent="0.25">
       <c r="A67" s="16" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="B67" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C67" s="14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D67" s="14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E67" s="16" t="s">
-        <v>239</v>
+        <v>197</v>
       </c>
       <c r="F67" s="19" t="s">
-        <v>249</v>
+        <v>315</v>
       </c>
       <c r="G67" s="18" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="H67" s="31" t="s">
-        <v>248</v>
+        <v>200</v>
       </c>
       <c r="I67" s="1"/>
       <c r="J67" s="1"/>
@@ -6023,28 +6023,28 @@
     </row>
     <row r="68" spans="1:11" ht="126" x14ac:dyDescent="0.25">
       <c r="A68" s="16" t="s">
-        <v>188</v>
+        <v>162</v>
       </c>
       <c r="B68" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C68" s="14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D68" s="14" t="s">
-        <v>254</v>
+        <v>316</v>
       </c>
       <c r="E68" s="16" t="s">
-        <v>255</v>
+        <v>317</v>
       </c>
       <c r="F68" s="19" t="s">
-        <v>250</v>
+        <v>318</v>
       </c>
       <c r="G68" s="18" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="H68" s="31" t="s">
-        <v>165</v>
+        <v>148</v>
       </c>
       <c r="I68" s="1"/>
       <c r="J68" s="1"/>
@@ -6071,8 +6071,8 @@
               <to>
                 <xdr:col>10</xdr:col>
                 <xdr:colOff>2971800</xdr:colOff>
-                <xdr:row>8</xdr:row>
-                <xdr:rowOff>1438275</xdr:rowOff>
+                <xdr:row>9</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
               </to>
             </anchor>
           </objectPr>
@@ -6096,8 +6096,8 @@
               <to>
                 <xdr:col>10</xdr:col>
                 <xdr:colOff>2971800</xdr:colOff>
-                <xdr:row>9</xdr:row>
-                <xdr:rowOff>1400175</xdr:rowOff>
+                <xdr:row>10</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
               </to>
             </anchor>
           </objectPr>
@@ -6121,8 +6121,8 @@
               <to>
                 <xdr:col>10</xdr:col>
                 <xdr:colOff>2971800</xdr:colOff>
-                <xdr:row>10</xdr:row>
-                <xdr:rowOff>1438275</xdr:rowOff>
+                <xdr:row>11</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
               </to>
             </anchor>
           </objectPr>
@@ -6146,8 +6146,8 @@
               <to>
                 <xdr:col>10</xdr:col>
                 <xdr:colOff>2971800</xdr:colOff>
-                <xdr:row>11</xdr:row>
-                <xdr:rowOff>1476375</xdr:rowOff>
+                <xdr:row>12</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
               </to>
             </anchor>
           </objectPr>
@@ -6171,8 +6171,8 @@
               <to>
                 <xdr:col>10</xdr:col>
                 <xdr:colOff>2971800</xdr:colOff>
-                <xdr:row>12</xdr:row>
-                <xdr:rowOff>1419225</xdr:rowOff>
+                <xdr:row>13</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
               </to>
             </anchor>
           </objectPr>
@@ -6196,8 +6196,8 @@
               <to>
                 <xdr:col>10</xdr:col>
                 <xdr:colOff>2971800</xdr:colOff>
-                <xdr:row>13</xdr:row>
-                <xdr:rowOff>1571625</xdr:rowOff>
+                <xdr:row>14</xdr:row>
+                <xdr:rowOff>171450</xdr:rowOff>
               </to>
             </anchor>
           </objectPr>
@@ -6221,8 +6221,8 @@
               <to>
                 <xdr:col>10</xdr:col>
                 <xdr:colOff>2971800</xdr:colOff>
-                <xdr:row>14</xdr:row>
-                <xdr:rowOff>1476375</xdr:rowOff>
+                <xdr:row>15</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
               </to>
             </anchor>
           </objectPr>
@@ -6246,8 +6246,8 @@
               <to>
                 <xdr:col>10</xdr:col>
                 <xdr:colOff>2971800</xdr:colOff>
-                <xdr:row>15</xdr:row>
-                <xdr:rowOff>1476375</xdr:rowOff>
+                <xdr:row>16</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
               </to>
             </anchor>
           </objectPr>
@@ -6271,8 +6271,8 @@
               <to>
                 <xdr:col>10</xdr:col>
                 <xdr:colOff>2971800</xdr:colOff>
-                <xdr:row>16</xdr:row>
-                <xdr:rowOff>1476375</xdr:rowOff>
+                <xdr:row>17</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
               </to>
             </anchor>
           </objectPr>
@@ -6296,8 +6296,8 @@
               <to>
                 <xdr:col>10</xdr:col>
                 <xdr:colOff>2971800</xdr:colOff>
-                <xdr:row>17</xdr:row>
-                <xdr:rowOff>1400175</xdr:rowOff>
+                <xdr:row>18</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
               </to>
             </anchor>
           </objectPr>
@@ -6321,8 +6321,8 @@
               <to>
                 <xdr:col>10</xdr:col>
                 <xdr:colOff>2971800</xdr:colOff>
-                <xdr:row>18</xdr:row>
-                <xdr:rowOff>1476375</xdr:rowOff>
+                <xdr:row>19</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
               </to>
             </anchor>
           </objectPr>
@@ -6346,8 +6346,8 @@
               <to>
                 <xdr:col>10</xdr:col>
                 <xdr:colOff>2971800</xdr:colOff>
-                <xdr:row>19</xdr:row>
-                <xdr:rowOff>1476375</xdr:rowOff>
+                <xdr:row>20</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
               </to>
             </anchor>
           </objectPr>
@@ -6396,8 +6396,8 @@
               <to>
                 <xdr:col>10</xdr:col>
                 <xdr:colOff>2714625</xdr:colOff>
-                <xdr:row>54</xdr:row>
-                <xdr:rowOff>1685925</xdr:rowOff>
+                <xdr:row>55</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
               </to>
             </anchor>
           </objectPr>
@@ -6421,8 +6421,8 @@
               <to>
                 <xdr:col>10</xdr:col>
                 <xdr:colOff>2714625</xdr:colOff>
-                <xdr:row>55</xdr:row>
-                <xdr:rowOff>1685925</xdr:rowOff>
+                <xdr:row>56</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
               </to>
             </anchor>
           </objectPr>
@@ -6446,8 +6446,8 @@
               <to>
                 <xdr:col>10</xdr:col>
                 <xdr:colOff>2714625</xdr:colOff>
-                <xdr:row>56</xdr:row>
-                <xdr:rowOff>1685925</xdr:rowOff>
+                <xdr:row>57</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
               </to>
             </anchor>
           </objectPr>
@@ -6471,8 +6471,8 @@
               <to>
                 <xdr:col>10</xdr:col>
                 <xdr:colOff>2714625</xdr:colOff>
-                <xdr:row>57</xdr:row>
-                <xdr:rowOff>1685925</xdr:rowOff>
+                <xdr:row>58</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
               </to>
             </anchor>
           </objectPr>
@@ -6496,8 +6496,8 @@
               <to>
                 <xdr:col>10</xdr:col>
                 <xdr:colOff>2714625</xdr:colOff>
-                <xdr:row>58</xdr:row>
-                <xdr:rowOff>1685925</xdr:rowOff>
+                <xdr:row>59</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
               </to>
             </anchor>
           </objectPr>
@@ -6521,8 +6521,8 @@
               <to>
                 <xdr:col>10</xdr:col>
                 <xdr:colOff>2714625</xdr:colOff>
-                <xdr:row>59</xdr:row>
-                <xdr:rowOff>1685925</xdr:rowOff>
+                <xdr:row>60</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
               </to>
             </anchor>
           </objectPr>
@@ -6546,8 +6546,8 @@
               <to>
                 <xdr:col>10</xdr:col>
                 <xdr:colOff>2714625</xdr:colOff>
-                <xdr:row>60</xdr:row>
-                <xdr:rowOff>1685925</xdr:rowOff>
+                <xdr:row>61</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
               </to>
             </anchor>
           </objectPr>
@@ -6571,8 +6571,8 @@
               <to>
                 <xdr:col>10</xdr:col>
                 <xdr:colOff>2714625</xdr:colOff>
-                <xdr:row>61</xdr:row>
-                <xdr:rowOff>1685925</xdr:rowOff>
+                <xdr:row>62</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
               </to>
             </anchor>
           </objectPr>
@@ -6631,12 +6631,12 @@
         <v>28</v>
       </c>
       <c r="L1" s="56" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:12" s="5" customFormat="1" ht="29.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="53" t="s">
-        <v>272</v>
+        <v>215</v>
       </c>
       <c r="B2" s="58">
         <v>7</v>
@@ -6674,10 +6674,10 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="50" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B3" s="44" t="s">
-        <v>273</v>
+        <v>216</v>
       </c>
       <c r="C3" s="57"/>
       <c r="D3" s="57"/>
@@ -6692,10 +6692,10 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="51" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B4" s="48" t="s">
-        <v>273</v>
+        <v>216</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
@@ -6710,10 +6710,10 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="51" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B5" s="48" t="s">
-        <v>273</v>
+        <v>216</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
@@ -6728,10 +6728,10 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="51" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B6" s="48" t="s">
-        <v>273</v>
+        <v>216</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
@@ -6746,10 +6746,10 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="51" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B7" s="48" t="s">
-        <v>273</v>
+        <v>216</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
@@ -6764,10 +6764,10 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="51" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="B8" s="48" t="s">
-        <v>273</v>
+        <v>216</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
@@ -6782,10 +6782,10 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="51" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="B9" s="48" t="s">
-        <v>273</v>
+        <v>216</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
@@ -6800,11 +6800,11 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="51" t="s">
-        <v>274</v>
+        <v>217</v>
       </c>
       <c r="B10" s="32"/>
       <c r="C10" s="10" t="s">
-        <v>273</v>
+        <v>216</v>
       </c>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
@@ -6818,11 +6818,11 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="51" t="s">
-        <v>275</v>
+        <v>218</v>
       </c>
       <c r="B11" s="32"/>
       <c r="C11" s="10" t="s">
-        <v>273</v>
+        <v>216</v>
       </c>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
@@ -6836,11 +6836,11 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="51" t="s">
-        <v>276</v>
+        <v>219</v>
       </c>
       <c r="B12" s="32"/>
       <c r="C12" s="10" t="s">
-        <v>273</v>
+        <v>216</v>
       </c>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
@@ -6854,11 +6854,11 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="51" t="s">
-        <v>277</v>
+        <v>220</v>
       </c>
       <c r="B13" s="32"/>
       <c r="C13" s="10" t="s">
-        <v>273</v>
+        <v>216</v>
       </c>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
@@ -6872,11 +6872,11 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="51" t="s">
-        <v>278</v>
+        <v>221</v>
       </c>
       <c r="B14" s="32"/>
       <c r="C14" s="10" t="s">
-        <v>273</v>
+        <v>216</v>
       </c>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
@@ -6890,11 +6890,11 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="51" t="s">
-        <v>279</v>
+        <v>222</v>
       </c>
       <c r="B15" s="32"/>
       <c r="C15" s="10" t="s">
-        <v>273</v>
+        <v>216</v>
       </c>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
@@ -6908,11 +6908,11 @@
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="51" t="s">
-        <v>280</v>
+        <v>223</v>
       </c>
       <c r="B16" s="32"/>
       <c r="C16" s="10" t="s">
-        <v>273</v>
+        <v>216</v>
       </c>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
@@ -6926,11 +6926,11 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="51" t="s">
-        <v>281</v>
+        <v>224</v>
       </c>
       <c r="B17" s="32"/>
       <c r="C17" s="10" t="s">
-        <v>273</v>
+        <v>216</v>
       </c>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
@@ -6944,11 +6944,11 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="51" t="s">
-        <v>282</v>
+        <v>225</v>
       </c>
       <c r="B18" s="32"/>
       <c r="C18" s="10" t="s">
-        <v>273</v>
+        <v>216</v>
       </c>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
@@ -6962,11 +6962,11 @@
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="51" t="s">
-        <v>283</v>
+        <v>226</v>
       </c>
       <c r="B19" s="32"/>
       <c r="C19" s="10" t="s">
-        <v>273</v>
+        <v>216</v>
       </c>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
@@ -6980,11 +6980,11 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="51" t="s">
-        <v>284</v>
+        <v>227</v>
       </c>
       <c r="B20" s="32"/>
       <c r="C20" s="10" t="s">
-        <v>273</v>
+        <v>216</v>
       </c>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
@@ -6998,11 +6998,11 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="51" t="s">
-        <v>285</v>
+        <v>228</v>
       </c>
       <c r="B21" s="32"/>
       <c r="C21" s="10" t="s">
-        <v>273</v>
+        <v>216</v>
       </c>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
@@ -7016,12 +7016,12 @@
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="51" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="B22" s="32"/>
       <c r="C22" s="1"/>
       <c r="D22" s="10" t="s">
-        <v>273</v>
+        <v>216</v>
       </c>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
@@ -7034,12 +7034,12 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="51" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B23" s="32"/>
       <c r="C23" s="1"/>
       <c r="D23" s="10" t="s">
-        <v>273</v>
+        <v>216</v>
       </c>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
@@ -7052,13 +7052,13 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="51" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="B24" s="32"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
       <c r="E24" s="10" t="s">
-        <v>273</v>
+        <v>216</v>
       </c>
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
@@ -7070,13 +7070,13 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="51" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="B25" s="32"/>
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
       <c r="E25" s="10" t="s">
-        <v>273</v>
+        <v>216</v>
       </c>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
@@ -7088,13 +7088,13 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="51" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="B26" s="32"/>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
       <c r="E26" s="10" t="s">
-        <v>273</v>
+        <v>216</v>
       </c>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
@@ -7106,13 +7106,13 @@
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="51" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="B27" s="32"/>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
       <c r="E27" s="10" t="s">
-        <v>273</v>
+        <v>216</v>
       </c>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
@@ -7124,14 +7124,14 @@
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="51" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="B28" s="32"/>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
       <c r="F28" s="10" t="s">
-        <v>273</v>
+        <v>216</v>
       </c>
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
@@ -7142,14 +7142,14 @@
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="51" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="B29" s="32"/>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
       <c r="F29" s="10" t="s">
-        <v>273</v>
+        <v>216</v>
       </c>
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
@@ -7160,14 +7160,14 @@
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="51" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="B30" s="32"/>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
       <c r="F30" s="10" t="s">
-        <v>273</v>
+        <v>216</v>
       </c>
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
@@ -7178,14 +7178,14 @@
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="51" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="B31" s="32"/>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
       <c r="F31" s="10" t="s">
-        <v>273</v>
+        <v>216</v>
       </c>
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
@@ -7196,7 +7196,7 @@
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="51" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="B32" s="32"/>
       <c r="C32" s="1"/>
@@ -7204,7 +7204,7 @@
       <c r="E32" s="1"/>
       <c r="F32" s="1"/>
       <c r="G32" s="10" t="s">
-        <v>273</v>
+        <v>216</v>
       </c>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
@@ -7214,7 +7214,7 @@
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" s="51" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="B33" s="32"/>
       <c r="C33" s="1"/>
@@ -7222,7 +7222,7 @@
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
       <c r="G33" s="10" t="s">
-        <v>273</v>
+        <v>216</v>
       </c>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
@@ -7232,7 +7232,7 @@
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="51" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="B34" s="32"/>
       <c r="C34" s="1"/>
@@ -7240,7 +7240,7 @@
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
       <c r="G34" s="10" t="s">
-        <v>273</v>
+        <v>216</v>
       </c>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
@@ -7250,7 +7250,7 @@
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="51" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="B35" s="32"/>
       <c r="C35" s="1"/>
@@ -7258,7 +7258,7 @@
       <c r="E35" s="1"/>
       <c r="F35" s="1"/>
       <c r="G35" s="10" t="s">
-        <v>273</v>
+        <v>216</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
@@ -7268,7 +7268,7 @@
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" s="51" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="B36" s="32"/>
       <c r="C36" s="1"/>
@@ -7277,7 +7277,7 @@
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
       <c r="H36" s="10" t="s">
-        <v>273</v>
+        <v>216</v>
       </c>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
@@ -7286,7 +7286,7 @@
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="51" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="B37" s="32"/>
       <c r="C37" s="1"/>
@@ -7296,7 +7296,7 @@
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
       <c r="I37" s="10" t="s">
-        <v>273</v>
+        <v>216</v>
       </c>
       <c r="J37" s="10"/>
       <c r="K37" s="1"/>
@@ -7304,7 +7304,7 @@
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="51" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="B38" s="32"/>
       <c r="C38" s="1"/>
@@ -7315,14 +7315,14 @@
       <c r="H38" s="1"/>
       <c r="I38" s="10"/>
       <c r="J38" s="10" t="s">
-        <v>273</v>
+        <v>216</v>
       </c>
       <c r="K38" s="1"/>
       <c r="L38" s="33"/>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="51" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="B39" s="32"/>
       <c r="C39" s="1"/>
@@ -7333,14 +7333,14 @@
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
       <c r="J39" s="10" t="s">
-        <v>273</v>
+        <v>216</v>
       </c>
       <c r="K39" s="1"/>
       <c r="L39" s="33"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" s="51" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="B40" s="32"/>
       <c r="C40" s="1"/>
@@ -7352,13 +7352,13 @@
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
       <c r="K40" s="10" t="s">
-        <v>273</v>
+        <v>216</v>
       </c>
       <c r="L40" s="33"/>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" s="51" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="B41" s="32"/>
       <c r="C41" s="1"/>
@@ -7370,13 +7370,13 @@
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
       <c r="K41" s="10" t="s">
-        <v>273</v>
+        <v>216</v>
       </c>
       <c r="L41" s="33"/>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" s="51" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="B42" s="32"/>
       <c r="C42" s="1"/>
@@ -7388,13 +7388,13 @@
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
       <c r="K42" s="10" t="s">
-        <v>273</v>
+        <v>216</v>
       </c>
       <c r="L42" s="33"/>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" s="51" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="B43" s="32"/>
       <c r="C43" s="1"/>
@@ -7406,13 +7406,13 @@
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
       <c r="K43" s="10" t="s">
-        <v>273</v>
+        <v>216</v>
       </c>
       <c r="L43" s="33"/>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" s="51" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="B44" s="32"/>
       <c r="C44" s="1"/>
@@ -7424,13 +7424,13 @@
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
       <c r="K44" s="10" t="s">
-        <v>273</v>
+        <v>216</v>
       </c>
       <c r="L44" s="33"/>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" s="51" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="B45" s="32"/>
       <c r="C45" s="1"/>
@@ -7442,13 +7442,13 @@
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
       <c r="K45" s="10" t="s">
-        <v>273</v>
+        <v>216</v>
       </c>
       <c r="L45" s="33"/>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" s="51" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="B46" s="32"/>
       <c r="C46" s="1"/>
@@ -7460,13 +7460,13 @@
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
       <c r="K46" s="10" t="s">
-        <v>273</v>
+        <v>216</v>
       </c>
       <c r="L46" s="33"/>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" s="51" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="B47" s="32"/>
       <c r="C47" s="1"/>
@@ -7478,13 +7478,13 @@
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
       <c r="K47" s="10" t="s">
-        <v>273</v>
+        <v>216</v>
       </c>
       <c r="L47" s="33"/>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" s="51" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="B48" s="32"/>
       <c r="C48" s="1"/>
@@ -7496,13 +7496,13 @@
       <c r="I48" s="1"/>
       <c r="J48" s="1"/>
       <c r="K48" s="10" t="s">
-        <v>273</v>
+        <v>216</v>
       </c>
       <c r="L48" s="33"/>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" s="51" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="B49" s="32"/>
       <c r="C49" s="1"/>
@@ -7514,13 +7514,13 @@
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
       <c r="K49" s="10" t="s">
-        <v>273</v>
+        <v>216</v>
       </c>
       <c r="L49" s="33"/>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" s="51" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="B50" s="32"/>
       <c r="C50" s="1"/>
@@ -7532,13 +7532,13 @@
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
       <c r="K50" s="10" t="s">
-        <v>273</v>
+        <v>216</v>
       </c>
       <c r="L50" s="33"/>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" s="51" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="B51" s="32"/>
       <c r="C51" s="1"/>
@@ -7550,13 +7550,13 @@
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
       <c r="K51" s="10" t="s">
-        <v>273</v>
+        <v>216</v>
       </c>
       <c r="L51" s="33"/>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" s="51" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="B52" s="32"/>
       <c r="C52" s="1"/>
@@ -7568,13 +7568,13 @@
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
       <c r="K52" s="10" t="s">
-        <v>273</v>
+        <v>216</v>
       </c>
       <c r="L52" s="33"/>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" s="51" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="B53" s="32"/>
       <c r="C53" s="1"/>
@@ -7586,13 +7586,13 @@
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
       <c r="K53" s="10" t="s">
-        <v>273</v>
+        <v>216</v>
       </c>
       <c r="L53" s="33"/>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" s="51" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="B54" s="32"/>
       <c r="C54" s="1"/>
@@ -7604,13 +7604,13 @@
       <c r="I54" s="1"/>
       <c r="J54" s="1"/>
       <c r="K54" s="10" t="s">
-        <v>273</v>
+        <v>216</v>
       </c>
       <c r="L54" s="33"/>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" s="51" t="s">
-        <v>295</v>
+        <v>238</v>
       </c>
       <c r="B55" s="32"/>
       <c r="C55" s="1"/>
@@ -7622,13 +7622,13 @@
       <c r="I55" s="1"/>
       <c r="J55" s="1"/>
       <c r="K55" s="10" t="s">
-        <v>273</v>
+        <v>216</v>
       </c>
       <c r="L55" s="33"/>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" s="51" t="s">
-        <v>296</v>
+        <v>239</v>
       </c>
       <c r="B56" s="32"/>
       <c r="C56" s="1"/>
@@ -7640,13 +7640,13 @@
       <c r="I56" s="1"/>
       <c r="J56" s="1"/>
       <c r="K56" s="10" t="s">
-        <v>273</v>
+        <v>216</v>
       </c>
       <c r="L56" s="33"/>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" s="51" t="s">
-        <v>297</v>
+        <v>240</v>
       </c>
       <c r="B57" s="32"/>
       <c r="C57" s="1"/>
@@ -7658,13 +7658,13 @@
       <c r="I57" s="1"/>
       <c r="J57" s="1"/>
       <c r="K57" s="10" t="s">
-        <v>273</v>
+        <v>216</v>
       </c>
       <c r="L57" s="33"/>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" s="51" t="s">
-        <v>298</v>
+        <v>241</v>
       </c>
       <c r="B58" s="32"/>
       <c r="C58" s="1"/>
@@ -7676,13 +7676,13 @@
       <c r="I58" s="1"/>
       <c r="J58" s="1"/>
       <c r="K58" s="10" t="s">
-        <v>273</v>
+        <v>216</v>
       </c>
       <c r="L58" s="33"/>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" s="51" t="s">
-        <v>299</v>
+        <v>242</v>
       </c>
       <c r="B59" s="32"/>
       <c r="C59" s="1"/>
@@ -7694,13 +7694,13 @@
       <c r="I59" s="1"/>
       <c r="J59" s="1"/>
       <c r="K59" s="10" t="s">
-        <v>273</v>
+        <v>216</v>
       </c>
       <c r="L59" s="33"/>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" s="51" t="s">
-        <v>300</v>
+        <v>243</v>
       </c>
       <c r="B60" s="32"/>
       <c r="C60" s="1"/>
@@ -7712,13 +7712,13 @@
       <c r="I60" s="1"/>
       <c r="J60" s="1"/>
       <c r="K60" s="10" t="s">
-        <v>273</v>
+        <v>216</v>
       </c>
       <c r="L60" s="33"/>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" s="51" t="s">
-        <v>301</v>
+        <v>244</v>
       </c>
       <c r="B61" s="32"/>
       <c r="C61" s="1"/>
@@ -7730,13 +7730,13 @@
       <c r="I61" s="1"/>
       <c r="J61" s="1"/>
       <c r="K61" s="10" t="s">
-        <v>273</v>
+        <v>216</v>
       </c>
       <c r="L61" s="33"/>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" s="51" t="s">
-        <v>302</v>
+        <v>245</v>
       </c>
       <c r="B62" s="32"/>
       <c r="C62" s="1"/>
@@ -7748,13 +7748,13 @@
       <c r="I62" s="1"/>
       <c r="J62" s="1"/>
       <c r="K62" s="10" t="s">
-        <v>273</v>
+        <v>216</v>
       </c>
       <c r="L62" s="33"/>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" s="51" t="s">
-        <v>303</v>
+        <v>246</v>
       </c>
       <c r="B63" s="32"/>
       <c r="C63" s="1"/>
@@ -7766,13 +7766,13 @@
       <c r="I63" s="1"/>
       <c r="J63" s="1"/>
       <c r="K63" s="10" t="s">
-        <v>273</v>
+        <v>216</v>
       </c>
       <c r="L63" s="33"/>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" s="51" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="B64" s="32"/>
       <c r="C64" s="1"/>
@@ -7784,13 +7784,13 @@
       <c r="I64" s="1"/>
       <c r="J64" s="1"/>
       <c r="K64" s="10" t="s">
-        <v>273</v>
+        <v>216</v>
       </c>
       <c r="L64" s="33"/>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65" s="51" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="B65" s="32"/>
       <c r="C65" s="1"/>
@@ -7802,13 +7802,13 @@
       <c r="I65" s="1"/>
       <c r="J65" s="1"/>
       <c r="K65" s="10" t="s">
-        <v>273</v>
+        <v>216</v>
       </c>
       <c r="L65" s="33"/>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" s="51" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="B66" s="32"/>
       <c r="C66" s="1"/>
@@ -7821,12 +7821,12 @@
       <c r="J66" s="1"/>
       <c r="K66" s="1"/>
       <c r="L66" s="45" t="s">
-        <v>273</v>
+        <v>216</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67" s="51" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="B67" s="32"/>
       <c r="C67" s="1"/>
@@ -7839,12 +7839,12 @@
       <c r="J67" s="1"/>
       <c r="K67" s="1"/>
       <c r="L67" s="45" t="s">
-        <v>273</v>
+        <v>216</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68" s="51" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="B68" s="32"/>
       <c r="C68" s="1"/>
@@ -7857,12 +7857,12 @@
       <c r="J68" s="1"/>
       <c r="K68" s="1"/>
       <c r="L68" s="45" t="s">
-        <v>273</v>
+        <v>216</v>
       </c>
     </row>
     <row r="69" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="52" t="s">
-        <v>188</v>
+        <v>162</v>
       </c>
       <c r="B69" s="49"/>
       <c r="C69" s="46"/>
@@ -7875,7 +7875,7 @@
       <c r="J69" s="46"/>
       <c r="K69" s="46"/>
       <c r="L69" s="47" t="s">
-        <v>273</v>
+        <v>216</v>
       </c>
     </row>
   </sheetData>
